--- a/Reports/teachers_names_shiraz2026.xlsx
+++ b/Reports/teachers_names_shiraz2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IMC_1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IMC_1\Documents\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FA5A2F-496D-43EF-95B8-3AEAB2178E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED7279B-C436-46F6-9369-FE1DFBD7F4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{001B96FF-34AA-45A7-A35C-B7BC922ACB0E}"/>
   </bookViews>
@@ -829,7 +829,7 @@
         <v>14111059</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E2" s="1">
         <v>33733</v>
@@ -852,7 +852,7 @@
         <v>14111059</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E3" s="1">
         <v>33672</v>
@@ -875,7 +875,7 @@
         <v>14111059</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E4" s="1">
         <v>41648</v>
@@ -898,7 +898,7 @@
         <v>14111031</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>75</v>
@@ -921,7 +921,7 @@
         <v>14111031</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E6" s="1">
         <v>39508</v>
@@ -944,7 +944,7 @@
         <v>14111031</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E7" s="1">
         <v>39352</v>
@@ -967,7 +967,7 @@
         <v>14111080</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>76</v>
@@ -990,7 +990,7 @@
         <v>14111080</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E9" s="1">
         <v>43199</v>
@@ -1013,7 +1013,7 @@
         <v>14111080</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E10" s="1">
         <v>36900</v>
@@ -1036,7 +1036,7 @@
         <v>14112146</v>
       </c>
       <c r="D11">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E11" s="1">
         <v>45572</v>
@@ -1059,7 +1059,7 @@
         <v>14112087</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E12" s="1">
         <v>35319</v>
@@ -1082,7 +1082,7 @@
         <v>14111118</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>77</v>
@@ -1105,7 +1105,7 @@
         <v>14111118</v>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>78</v>
@@ -1128,7 +1128,7 @@
         <v>14111118</v>
       </c>
       <c r="D15">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E15" s="1">
         <v>41551</v>
@@ -1151,7 +1151,7 @@
         <v>14112068</v>
       </c>
       <c r="D16">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>79</v>
@@ -1174,7 +1174,7 @@
         <v>14112068</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>80</v>
@@ -1197,7 +1197,7 @@
         <v>14111128</v>
       </c>
       <c r="D18">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E18" s="1">
         <v>40910</v>
@@ -1220,7 +1220,7 @@
         <v>14111104</v>
       </c>
       <c r="D19">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
@@ -1243,7 +1243,7 @@
         <v>14111104</v>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E20" s="1">
         <v>39939</v>
@@ -1266,7 +1266,7 @@
         <v>14112016</v>
       </c>
       <c r="D21">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>82</v>
@@ -1289,7 +1289,7 @@
         <v>14111143</v>
       </c>
       <c r="D22">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>83</v>
@@ -1312,7 +1312,7 @@
         <v>14111084</v>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>84</v>
@@ -1335,7 +1335,7 @@
         <v>14111084</v>
       </c>
       <c r="D24">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E24" s="1">
         <v>43991</v>
@@ -1358,7 +1358,7 @@
         <v>14112044</v>
       </c>
       <c r="D25">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E25" s="1">
         <v>39700</v>
@@ -1381,7 +1381,7 @@
         <v>14112028</v>
       </c>
       <c r="D26">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E26" s="1">
         <v>43322</v>
@@ -1404,7 +1404,7 @@
         <v>14112039</v>
       </c>
       <c r="D27">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>85</v>
@@ -1427,7 +1427,7 @@
         <v>14112039</v>
       </c>
       <c r="D28">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>86</v>
@@ -1450,7 +1450,7 @@
         <v>14112009</v>
       </c>
       <c r="D29">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E29" s="1">
         <v>37630</v>
@@ -1473,7 +1473,7 @@
         <v>14112009</v>
       </c>
       <c r="D30">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>87</v>
@@ -1496,7 +1496,7 @@
         <v>14112009</v>
       </c>
       <c r="D31">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>88</v>
@@ -1522,7 +1522,7 @@
         <v>14112038</v>
       </c>
       <c r="D32">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E32" s="1">
         <v>37689</v>
@@ -1545,7 +1545,7 @@
         <v>14112009</v>
       </c>
       <c r="D33">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E33" s="1">
         <v>39122</v>
@@ -1568,7 +1568,7 @@
         <v>14112038</v>
       </c>
       <c r="D34">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E34" s="1">
         <v>40278</v>
@@ -1591,7 +1591,7 @@
         <v>14112124</v>
       </c>
       <c r="D35">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>89</v>
@@ -1614,7 +1614,7 @@
         <v>14112140</v>
       </c>
       <c r="D36">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E36" s="1">
         <v>39395</v>
@@ -1637,7 +1637,7 @@
         <v>14112140</v>
       </c>
       <c r="D37">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E37" s="1">
         <v>40065</v>
@@ -1660,7 +1660,7 @@
         <v>14112105</v>
       </c>
       <c r="D38">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>90</v>
@@ -1683,7 +1683,7 @@
         <v>14112105</v>
       </c>
       <c r="D39">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>91</v>
@@ -1706,7 +1706,7 @@
         <v>14112045</v>
       </c>
       <c r="D40">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E40" s="1">
         <v>37233</v>
@@ -1729,7 +1729,7 @@
         <v>14112090</v>
       </c>
       <c r="D41">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>92</v>
@@ -1752,7 +1752,7 @@
         <v>14112090</v>
       </c>
       <c r="D42">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>93</v>
@@ -1775,7 +1775,7 @@
         <v>14112135</v>
       </c>
       <c r="D43">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>94</v>
@@ -1798,7 +1798,7 @@
         <v>14112135</v>
       </c>
       <c r="D44">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E44" s="1">
         <v>37996</v>
@@ -1821,7 +1821,7 @@
         <v>14111043</v>
       </c>
       <c r="D45">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>95</v>
@@ -1844,7 +1844,7 @@
         <v>14112146</v>
       </c>
       <c r="D46">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E46" s="1">
         <v>39700</v>
@@ -1867,7 +1867,7 @@
         <v>14112146</v>
       </c>
       <c r="D47">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>96</v>
@@ -1890,7 +1890,7 @@
         <v>14112134</v>
       </c>
       <c r="D48">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>97</v>
@@ -1913,7 +1913,7 @@
         <v>14112132</v>
       </c>
       <c r="D49">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>98</v>
@@ -1936,7 +1936,7 @@
         <v>14112132</v>
       </c>
       <c r="D50">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>99</v>
@@ -1959,7 +1959,7 @@
         <v>14112145</v>
       </c>
       <c r="D51">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>100</v>
@@ -1982,7 +1982,7 @@
         <v>14112145</v>
       </c>
       <c r="D52">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>101</v>
@@ -2005,7 +2005,7 @@
         <v>14111005</v>
       </c>
       <c r="D53">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E53" s="1">
         <v>39974</v>
@@ -2028,7 +2028,7 @@
         <v>14111005</v>
       </c>
       <c r="D54">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E54" s="1">
         <v>40888</v>
@@ -2051,7 +2051,7 @@
         <v>14111043</v>
       </c>
       <c r="D55">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>102</v>
@@ -2074,7 +2074,7 @@
         <v>14112012</v>
       </c>
       <c r="D56">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E56" s="1">
         <v>45544</v>
@@ -2097,7 +2097,7 @@
         <v>14112133</v>
       </c>
       <c r="D57">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E57" s="1">
         <v>45690</v>
@@ -2120,7 +2120,7 @@
         <v>14112133</v>
       </c>
       <c r="D58">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>103</v>
@@ -2143,7 +2143,7 @@
         <v>14112048</v>
       </c>
       <c r="D59">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>104</v>
@@ -2166,7 +2166,7 @@
         <v>14112048</v>
       </c>
       <c r="D60">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E60" s="1">
         <v>43384</v>
@@ -2189,7 +2189,7 @@
         <v>14112049</v>
       </c>
       <c r="D61">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>105</v>
@@ -2212,7 +2212,7 @@
         <v>14112049</v>
       </c>
       <c r="D62">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>106</v>
@@ -2235,7 +2235,7 @@
         <v>14112041</v>
       </c>
       <c r="D63">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>107</v>
@@ -2258,7 +2258,7 @@
         <v>14112041</v>
       </c>
       <c r="D64">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>108</v>
@@ -2281,7 +2281,7 @@
         <v>14112045</v>
       </c>
       <c r="D65">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>109</v>
@@ -2304,7 +2304,7 @@
         <v>14112049</v>
       </c>
       <c r="D66">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E66" s="1">
         <v>45536</v>
@@ -2327,7 +2327,7 @@
         <v>14112040</v>
       </c>
       <c r="D67">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E67" s="1">
         <v>41910</v>
@@ -2350,7 +2350,7 @@
         <v>14112074</v>
       </c>
       <c r="D68">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E68" s="1">
         <v>45916</v>
@@ -2373,7 +2373,7 @@
         <v>14112028</v>
       </c>
       <c r="D69">
-        <v>34</v>
+        <v>850644378</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>110</v>

--- a/Reports/teachers_names_shiraz2026.xlsx
+++ b/Reports/teachers_names_shiraz2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IMC_1\Documents\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED7279B-C436-46F6-9369-FE1DFBD7F4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80B3C55-5B70-49E4-8793-715DCD80FA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{001B96FF-34AA-45A7-A35C-B7BC922ACB0E}"/>
   </bookViews>
@@ -284,9 +284,6 @@
     <t>29/09/2024</t>
   </si>
   <si>
-    <t>28/8/2019</t>
-  </si>
-  <si>
     <t>26/09/2002</t>
   </si>
   <si>
@@ -311,9 +308,6 @@
     <t>23/08/2017</t>
   </si>
   <si>
-    <t>26/82013</t>
-  </si>
-  <si>
     <t>23/08/2003</t>
   </si>
   <si>
@@ -326,54 +320,9 @@
     <t>20/10/2020</t>
   </si>
   <si>
-    <t>21/8/2023</t>
-  </si>
-  <si>
-    <t>31/8/2003</t>
-  </si>
-  <si>
-    <t>30/8/2021</t>
-  </si>
-  <si>
-    <t>25/9/2007</t>
-  </si>
-  <si>
-    <t>15/8/2021</t>
-  </si>
-  <si>
-    <t>20/8/2005</t>
-  </si>
-  <si>
-    <t>20/9/2011</t>
-  </si>
-  <si>
-    <t>22/8/2019</t>
-  </si>
-  <si>
-    <t>23/9/2013</t>
-  </si>
-  <si>
-    <t>14/9/2009</t>
-  </si>
-  <si>
-    <t>18/9/2004</t>
-  </si>
-  <si>
-    <t>21/8/2019</t>
-  </si>
-  <si>
-    <t>27/9/2009</t>
-  </si>
-  <si>
     <t>22/12/2020</t>
   </si>
   <si>
-    <t>19/3/2018</t>
-  </si>
-  <si>
-    <t>14/9/2021</t>
-  </si>
-  <si>
     <t>بكالوريوس</t>
   </si>
   <si>
@@ -405,6 +354,57 @@
   </si>
   <si>
     <t>4112041 </t>
+  </si>
+  <si>
+    <t>26/08/2013</t>
+  </si>
+  <si>
+    <t>21/08/2023</t>
+  </si>
+  <si>
+    <t>31/08/2003</t>
+  </si>
+  <si>
+    <t>30/08/2021</t>
+  </si>
+  <si>
+    <t>25/09/2007</t>
+  </si>
+  <si>
+    <t>15/08/2021</t>
+  </si>
+  <si>
+    <t>20/08/2005</t>
+  </si>
+  <si>
+    <t>20/09/2011</t>
+  </si>
+  <si>
+    <t>22/08/2019</t>
+  </si>
+  <si>
+    <t>23/09/2013</t>
+  </si>
+  <si>
+    <t>14/09/2009</t>
+  </si>
+  <si>
+    <t>18/09/2004</t>
+  </si>
+  <si>
+    <t>21/08/2019</t>
+  </si>
+  <si>
+    <t>27/09/2009</t>
+  </si>
+  <si>
+    <t>19/03/2018</t>
+  </si>
+  <si>
+    <t>14/09/2021</t>
+  </si>
+  <si>
+    <t>28/08/2019</t>
   </si>
 </sst>
 </file>
@@ -449,11 +449,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -791,7 +796,9 @@
   <dimension ref="A1:L69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="16.33203125" customWidth="1"/>
+    <col min="1" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="3" customWidth="1"/>
+    <col min="6" max="8" width="16.33203125" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -808,7 +815,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -819,1570 +826,1570 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>980755052</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>14111059</v>
       </c>
       <c r="D2">
         <v>850644378</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="4">
         <v>33733</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>968485078</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>14111059</v>
       </c>
       <c r="D3">
         <v>850644378</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="4">
         <v>33672</v>
       </c>
       <c r="F3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>850091158</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>14111059</v>
       </c>
       <c r="D4">
         <v>850644378</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="4">
         <v>41648</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>938097144</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>14111031</v>
       </c>
       <c r="D5">
         <v>850644378</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="4" t="s">
         <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>900459736</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>14111031</v>
       </c>
       <c r="D6">
         <v>850644378</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="4">
         <v>39508</v>
       </c>
       <c r="F6" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G6" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>907943997</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>14111031</v>
       </c>
       <c r="D7">
         <v>850644378</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="4">
         <v>39352</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G7" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>906461728</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>14111080</v>
       </c>
       <c r="D8">
         <v>850644378</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G8" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>910454214</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>14111080</v>
       </c>
       <c r="D9">
         <v>850644378</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="4">
         <v>43199</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G9" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>913216859</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>14111080</v>
       </c>
       <c r="D10">
         <v>850644378</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="4">
         <v>36900</v>
       </c>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>406359927</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>14112146</v>
       </c>
       <c r="D11">
         <v>850644378</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="4">
         <v>45572</v>
       </c>
       <c r="F11" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>977865948</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>14112087</v>
       </c>
       <c r="D12">
         <v>850644378</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="4">
         <v>35319</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>401825245</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>14111118</v>
       </c>
       <c r="D13">
         <v>850644378</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="4" t="s">
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>853276004</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>14111118</v>
       </c>
       <c r="D14">
         <v>850644378</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>913202164</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>14111118</v>
       </c>
       <c r="D15">
         <v>850644378</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="4">
         <v>41551</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>945665354</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>14112068</v>
       </c>
       <c r="D16">
         <v>850644378</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="4" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>859709644</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>14112068</v>
       </c>
       <c r="D17">
         <v>850644378</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>939383568</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>14111128</v>
       </c>
       <c r="D18">
         <v>850644378</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="4">
         <v>40910</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>853040657</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>14111104</v>
       </c>
       <c r="D19">
         <v>850644378</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>81</v>
+      <c r="E19" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G19" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>973110670</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>14111104</v>
       </c>
       <c r="D20">
         <v>850644378</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="4">
         <v>39939</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>900064205</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>14112016</v>
       </c>
       <c r="D21">
         <v>850644378</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>82</v>
+      <c r="E21" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>853572311</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>14111143</v>
       </c>
       <c r="D22">
         <v>850644378</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>83</v>
+      <c r="E22" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>403423981</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>14111084</v>
       </c>
       <c r="D23">
         <v>850644378</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>84</v>
+      <c r="E23" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>406474395</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>14111084</v>
       </c>
       <c r="D24">
         <v>850644378</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="4">
         <v>43991</v>
       </c>
       <c r="F24" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>410698427</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <v>14112044</v>
       </c>
       <c r="D25">
         <v>850644378</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="4">
         <v>39700</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>949567580</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>14112028</v>
       </c>
       <c r="D26">
         <v>850644378</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="4">
         <v>43322</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>919094060</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="1">
         <v>14112039</v>
       </c>
       <c r="D27">
         <v>850644378</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>85</v>
+      <c r="E27" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>902442078</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="1">
         <v>14112039</v>
       </c>
       <c r="D28">
         <v>850644378</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>86</v>
+      <c r="E28" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>907586069</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>14112009</v>
       </c>
       <c r="D29">
         <v>850644378</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="4">
         <v>37630</v>
       </c>
       <c r="F29" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G29" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>907942197</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="1">
         <v>14112009</v>
       </c>
       <c r="D30">
         <v>850644378</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>87</v>
+      <c r="E30" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>902389196</v>
       </c>
       <c r="B31" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="1">
         <v>14112009</v>
       </c>
       <c r="D31">
         <v>850644378</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>88</v>
+      <c r="E31" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>941512303</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="1">
         <v>14112038</v>
       </c>
       <c r="D32">
         <v>850644378</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="4">
         <v>37689</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>850202847</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="1">
         <v>14112009</v>
       </c>
       <c r="D33">
         <v>850644378</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="4">
         <v>39122</v>
       </c>
       <c r="F33" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>904969409</v>
       </c>
       <c r="B34" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>14112038</v>
       </c>
       <c r="D34">
         <v>850644378</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="4">
         <v>40278</v>
       </c>
       <c r="F34" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>911686699</v>
       </c>
       <c r="B35" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="1">
         <v>14112124</v>
       </c>
       <c r="D35">
         <v>850644378</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>89</v>
+      <c r="E35" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="F35" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>984961466</v>
       </c>
       <c r="B36" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="1">
         <v>14112140</v>
       </c>
       <c r="D36">
         <v>850644378</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="4">
         <v>39395</v>
       </c>
       <c r="F36" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>852302116</v>
       </c>
       <c r="B37" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
         <v>14112140</v>
       </c>
       <c r="D37">
         <v>850644378</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="4">
         <v>40065</v>
       </c>
       <c r="F37" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>904994597</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="1">
         <v>14112105</v>
       </c>
       <c r="D38">
         <v>850644378</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>90</v>
+      <c r="E38" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="F38" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>900122409</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="1">
         <v>14112105</v>
       </c>
       <c r="D39">
         <v>850644378</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>91</v>
+      <c r="E39" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="F39" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G39" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>953107901</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="1">
         <v>14112045</v>
       </c>
       <c r="D40">
         <v>850644378</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="4">
         <v>37233</v>
       </c>
       <c r="F40" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>403826068</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="1">
         <v>14112090</v>
       </c>
       <c r="D41">
         <v>850644378</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>92</v>
+      <c r="E41" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="F41" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>989552252</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="1">
         <v>14112090</v>
       </c>
       <c r="D42">
         <v>850644378</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>93</v>
+      <c r="E42" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="F42" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="G42" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>852192368</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="1">
         <v>14112135</v>
       </c>
       <c r="D43">
         <v>850644378</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>94</v>
+      <c r="E43" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G43" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>911683332</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="1">
         <v>14112135</v>
       </c>
       <c r="D44">
         <v>850644378</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="4">
         <v>37996</v>
       </c>
       <c r="F44" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>858970445</v>
       </c>
       <c r="B45" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="1">
         <v>14111043</v>
       </c>
       <c r="D45">
         <v>850644378</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45" t="s">
         <v>95</v>
       </c>
-      <c r="F45" t="s">
-        <v>112</v>
-      </c>
       <c r="G45" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>994329175</v>
       </c>
       <c r="B46" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="1">
         <v>14112146</v>
       </c>
       <c r="D46">
         <v>850644378</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="4">
         <v>39700</v>
       </c>
       <c r="F46" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>954240850</v>
       </c>
       <c r="B47" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="1">
         <v>14112146</v>
       </c>
       <c r="D47">
         <v>850644378</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>96</v>
+      <c r="E47" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G47" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>401555594</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="1">
         <v>14112134</v>
       </c>
       <c r="D48">
         <v>850644378</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>97</v>
+      <c r="E48" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>907952691</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="1">
         <v>14112132</v>
       </c>
       <c r="D49">
         <v>850644378</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>98</v>
+      <c r="E49" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="F49" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G49" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>402189757</v>
       </c>
       <c r="B50" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="1">
         <v>14112132</v>
       </c>
       <c r="D50">
         <v>850644378</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>99</v>
+      <c r="E50" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="F50" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>912621182</v>
       </c>
       <c r="B51" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="1">
         <v>14112145</v>
       </c>
       <c r="D51">
         <v>850644378</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>100</v>
+      <c r="E51" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G51" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>997950167</v>
       </c>
       <c r="B52" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="1">
         <v>14112145</v>
       </c>
       <c r="D52">
         <v>850644378</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>101</v>
+      <c r="E52" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="F52" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>851544346</v>
       </c>
       <c r="B53" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="1">
         <v>14111005</v>
       </c>
       <c r="D53">
         <v>850644378</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="4">
         <v>39974</v>
       </c>
       <c r="F53" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G53" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>851723775</v>
       </c>
       <c r="B54" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="1">
         <v>14111005</v>
       </c>
       <c r="D54">
         <v>850644378</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="4">
         <v>40888</v>
       </c>
       <c r="F54" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G54" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>853977841</v>
       </c>
       <c r="B55" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="1">
         <v>14111043</v>
       </c>
       <c r="D55">
         <v>850644378</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>102</v>
+      <c r="E55" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="F55" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G55" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>401012653</v>
       </c>
       <c r="B56" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="1">
         <v>14112012</v>
       </c>
       <c r="D56">
         <v>850644378</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="4">
         <v>45544</v>
       </c>
       <c r="F56" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G56" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>854879103</v>
       </c>
       <c r="B57" t="s">
         <v>62</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="1">
         <v>14112133</v>
       </c>
       <c r="D57">
         <v>850644378</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="4">
         <v>45690</v>
       </c>
       <c r="F57" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>850379611</v>
       </c>
       <c r="B58" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="1">
         <v>14112133</v>
       </c>
       <c r="D58">
         <v>850644378</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>103</v>
+      <c r="E58" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G58" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>927702787</v>
       </c>
       <c r="B59" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="1">
         <v>14112048</v>
       </c>
       <c r="D59">
         <v>850644378</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>104</v>
+      <c r="E59" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="F59" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>906832084</v>
       </c>
       <c r="B60" t="s">
         <v>65</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="1">
         <v>14112048</v>
       </c>
       <c r="D60">
         <v>850644378</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="4">
         <v>43384</v>
       </c>
       <c r="F60" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G60" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>946826138</v>
       </c>
       <c r="B61" t="s">
         <v>66</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="1">
         <v>14112049</v>
       </c>
       <c r="D61">
         <v>850644378</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>105</v>
+      <c r="E61" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="F61" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G61" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>854136140</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="1">
         <v>14112049</v>
       </c>
       <c r="D62">
         <v>850644378</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>106</v>
+      <c r="E62" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="F62" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>939380949</v>
       </c>
       <c r="B63" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="1">
         <v>14112041</v>
       </c>
       <c r="D63">
         <v>850644378</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>107</v>
+      <c r="E63" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="F63" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G63" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>853214500</v>
       </c>
       <c r="B64" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="1">
         <v>14112041</v>
       </c>
       <c r="D64">
         <v>850644378</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>108</v>
+      <c r="E64" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="F64" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G64" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>984961474</v>
       </c>
       <c r="B65" t="s">
         <v>70</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="1">
         <v>14112045</v>
       </c>
       <c r="D65">
         <v>850644378</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>109</v>
+      <c r="E65" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="F65" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G65" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>858609795</v>
       </c>
       <c r="B66" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="1">
         <v>14112049</v>
       </c>
       <c r="D66">
         <v>850644378</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="4">
         <v>45536</v>
       </c>
       <c r="F66" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G66" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>936853365</v>
       </c>
       <c r="B67" t="s">
         <v>72</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="1">
         <v>14112040</v>
       </c>
       <c r="D67">
         <v>850644378</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="4">
         <v>41910</v>
       </c>
       <c r="F67" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G67" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>403420359</v>
       </c>
       <c r="B68" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="1">
         <v>14112074</v>
       </c>
       <c r="D68">
         <v>850644378</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="4">
         <v>45916</v>
       </c>
       <c r="F68" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>401485187</v>
       </c>
       <c r="B69" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="1">
         <v>14112028</v>
       </c>
       <c r="D69">
         <v>850644378</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>110</v>
+      <c r="E69" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="F69" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G69" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/teachers_names_shiraz2026.xlsx
+++ b/Reports/teachers_names_shiraz2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IMC_1\Documents\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80B3C55-5B70-49E4-8793-715DCD80FA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DDF1C8-EF3D-405E-9D58-5CE7A545B0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{001B96FF-34AA-45A7-A35C-B7BC922ACB0E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="143">
   <si>
     <t>Teacher_id</t>
   </si>
@@ -353,9 +353,6 @@
     <t xml:space="preserve">أدب </t>
   </si>
   <si>
-    <t>4112041 </t>
-  </si>
-  <si>
     <t>26/08/2013</t>
   </si>
   <si>
@@ -405,6 +402,72 @@
   </si>
   <si>
     <t>28/08/2019</t>
+  </si>
+  <si>
+    <t>score1</t>
+  </si>
+  <si>
+    <t>score2</t>
+  </si>
+  <si>
+    <t>score3</t>
+  </si>
+  <si>
+    <t>score4</t>
+  </si>
+  <si>
+    <t>score5</t>
+  </si>
+  <si>
+    <t>score6</t>
+  </si>
+  <si>
+    <t>score7</t>
+  </si>
+  <si>
+    <t>score8</t>
+  </si>
+  <si>
+    <t>score9</t>
+  </si>
+  <si>
+    <t>score10</t>
+  </si>
+  <si>
+    <t>score11</t>
+  </si>
+  <si>
+    <t>score12</t>
+  </si>
+  <si>
+    <t>score13</t>
+  </si>
+  <si>
+    <t>score14</t>
+  </si>
+  <si>
+    <t>score15</t>
+  </si>
+  <si>
+    <t>score16</t>
+  </si>
+  <si>
+    <t>score17</t>
+  </si>
+  <si>
+    <t>score18</t>
+  </si>
+  <si>
+    <t>score19</t>
+  </si>
+  <si>
+    <t>score20</t>
+  </si>
+  <si>
+    <t>score21</t>
+  </si>
+  <si>
+    <t>score22</t>
   </si>
 </sst>
 </file>
@@ -414,7 +477,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,10 +486,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFB91C1C"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -437,12 +504,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -452,12 +534,15 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -793,16 +878,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7382AA-1F78-4156-8AD8-EAD77507558A}">
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="2" customWidth="1"/>
     <col min="6" max="8" width="16.33203125" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -815,7 +900,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -824,8 +909,74 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" t="s">
+        <v>126</v>
+      </c>
+      <c r="N1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R1" t="s">
+        <v>131</v>
+      </c>
+      <c r="S1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T1" t="s">
+        <v>133</v>
+      </c>
+      <c r="U1" t="s">
+        <v>134</v>
+      </c>
+      <c r="V1" t="s">
+        <v>135</v>
+      </c>
+      <c r="W1" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>142</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>980755052</v>
       </c>
@@ -838,7 +989,7 @@
       <c r="D2">
         <v>850644378</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>33733</v>
       </c>
       <c r="F2" t="s">
@@ -847,8 +998,74 @@
       <c r="G2" t="s">
         <v>97</v>
       </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4">
+        <v>6</v>
+      </c>
+      <c r="K2" s="4">
+        <v>6</v>
+      </c>
+      <c r="L2" s="4">
+        <v>6</v>
+      </c>
+      <c r="M2" s="4">
+        <v>4</v>
+      </c>
+      <c r="N2" s="4">
+        <v>3</v>
+      </c>
+      <c r="O2" s="4">
+        <v>2</v>
+      </c>
+      <c r="P2" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>5</v>
+      </c>
+      <c r="R2" s="4">
+        <v>3</v>
+      </c>
+      <c r="S2" s="4">
+        <v>5</v>
+      </c>
+      <c r="T2" s="4">
+        <v>6</v>
+      </c>
+      <c r="U2" s="4">
+        <v>3</v>
+      </c>
+      <c r="V2" s="4">
+        <v>3</v>
+      </c>
+      <c r="W2" s="4">
+        <v>4</v>
+      </c>
+      <c r="X2" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>968485078</v>
       </c>
@@ -861,7 +1078,7 @@
       <c r="D3">
         <v>850644378</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>33672</v>
       </c>
       <c r="F3" t="s">
@@ -870,8 +1087,74 @@
       <c r="G3" t="s">
         <v>97</v>
       </c>
+      <c r="H3" s="4">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4">
+        <v>7</v>
+      </c>
+      <c r="K3" s="4">
+        <v>6</v>
+      </c>
+      <c r="L3" s="4">
+        <v>6</v>
+      </c>
+      <c r="M3" s="4">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>3</v>
+      </c>
+      <c r="O3" s="4">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>4</v>
+      </c>
+      <c r="R3" s="4">
+        <v>3</v>
+      </c>
+      <c r="S3" s="4">
+        <v>5</v>
+      </c>
+      <c r="T3" s="4">
+        <v>6</v>
+      </c>
+      <c r="U3" s="4">
+        <v>3</v>
+      </c>
+      <c r="V3" s="4">
+        <v>3</v>
+      </c>
+      <c r="W3" s="4">
+        <v>4</v>
+      </c>
+      <c r="X3" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>850091158</v>
       </c>
@@ -884,7 +1167,7 @@
       <c r="D4">
         <v>850644378</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>41648</v>
       </c>
       <c r="F4" t="s">
@@ -893,8 +1176,74 @@
       <c r="G4" t="s">
         <v>97</v>
       </c>
+      <c r="H4" s="4">
+        <v>4</v>
+      </c>
+      <c r="I4" s="4">
+        <v>6</v>
+      </c>
+      <c r="J4" s="4">
+        <v>7</v>
+      </c>
+      <c r="K4" s="4">
+        <v>6</v>
+      </c>
+      <c r="L4" s="4">
+        <v>5</v>
+      </c>
+      <c r="M4" s="4">
+        <v>5</v>
+      </c>
+      <c r="N4" s="4">
+        <v>3</v>
+      </c>
+      <c r="O4" s="4">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>5</v>
+      </c>
+      <c r="R4" s="4">
+        <v>4</v>
+      </c>
+      <c r="S4" s="4">
+        <v>5</v>
+      </c>
+      <c r="T4" s="4">
+        <v>5</v>
+      </c>
+      <c r="U4" s="4">
+        <v>3</v>
+      </c>
+      <c r="V4" s="4">
+        <v>3</v>
+      </c>
+      <c r="W4" s="4">
+        <v>4</v>
+      </c>
+      <c r="X4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>938097144</v>
       </c>
@@ -907,7 +1256,7 @@
       <c r="D5">
         <v>850644378</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F5" t="s">
@@ -916,8 +1265,74 @@
       <c r="G5" t="s">
         <v>98</v>
       </c>
+      <c r="H5" s="4">
+        <v>5</v>
+      </c>
+      <c r="I5" s="4">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4">
+        <v>7</v>
+      </c>
+      <c r="K5" s="4">
+        <v>6</v>
+      </c>
+      <c r="L5" s="4">
+        <v>6</v>
+      </c>
+      <c r="M5" s="4">
+        <v>5</v>
+      </c>
+      <c r="N5" s="4">
+        <v>2</v>
+      </c>
+      <c r="O5" s="4">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4">
+        <v>2</v>
+      </c>
+      <c r="S5" s="4">
+        <v>5</v>
+      </c>
+      <c r="T5" s="4">
+        <v>5</v>
+      </c>
+      <c r="U5" s="4">
+        <v>3</v>
+      </c>
+      <c r="V5" s="4">
+        <v>3</v>
+      </c>
+      <c r="W5" s="4">
+        <v>4</v>
+      </c>
+      <c r="X5" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>900459736</v>
       </c>
@@ -930,7 +1345,7 @@
       <c r="D6">
         <v>850644378</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>39508</v>
       </c>
       <c r="F6" t="s">
@@ -939,8 +1354,74 @@
       <c r="G6" t="s">
         <v>97</v>
       </c>
+      <c r="H6" s="4">
+        <v>4</v>
+      </c>
+      <c r="I6" s="4">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4">
+        <v>7</v>
+      </c>
+      <c r="K6" s="4">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4">
+        <v>6</v>
+      </c>
+      <c r="M6" s="4">
+        <v>4</v>
+      </c>
+      <c r="N6" s="4">
+        <v>2</v>
+      </c>
+      <c r="O6" s="4">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>5</v>
+      </c>
+      <c r="R6" s="4">
+        <v>4</v>
+      </c>
+      <c r="S6" s="4">
+        <v>6</v>
+      </c>
+      <c r="T6" s="4">
+        <v>4</v>
+      </c>
+      <c r="U6" s="4">
+        <v>3</v>
+      </c>
+      <c r="V6" s="4">
+        <v>3</v>
+      </c>
+      <c r="W6" s="4">
+        <v>4</v>
+      </c>
+      <c r="X6" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>907943997</v>
       </c>
@@ -953,7 +1434,7 @@
       <c r="D7">
         <v>850644378</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>39352</v>
       </c>
       <c r="F7" t="s">
@@ -962,8 +1443,74 @@
       <c r="G7" t="s">
         <v>97</v>
       </c>
+      <c r="H7" s="4">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4">
+        <v>6</v>
+      </c>
+      <c r="J7" s="4">
+        <v>7</v>
+      </c>
+      <c r="K7" s="4">
+        <v>6</v>
+      </c>
+      <c r="L7" s="4">
+        <v>5</v>
+      </c>
+      <c r="M7" s="4">
+        <v>5</v>
+      </c>
+      <c r="N7" s="4">
+        <v>3</v>
+      </c>
+      <c r="O7" s="4">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>4</v>
+      </c>
+      <c r="R7" s="4">
+        <v>3</v>
+      </c>
+      <c r="S7" s="4">
+        <v>5</v>
+      </c>
+      <c r="T7" s="4">
+        <v>4</v>
+      </c>
+      <c r="U7" s="4">
+        <v>3</v>
+      </c>
+      <c r="V7" s="4">
+        <v>3</v>
+      </c>
+      <c r="W7" s="4">
+        <v>4</v>
+      </c>
+      <c r="X7" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>906461728</v>
       </c>
@@ -976,7 +1523,7 @@
       <c r="D8">
         <v>850644378</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F8" t="s">
@@ -985,8 +1532,74 @@
       <c r="G8" t="s">
         <v>99</v>
       </c>
+      <c r="H8" s="4">
+        <v>5</v>
+      </c>
+      <c r="I8" s="4">
+        <v>7</v>
+      </c>
+      <c r="J8" s="4">
+        <v>7</v>
+      </c>
+      <c r="K8" s="4">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4">
+        <v>6</v>
+      </c>
+      <c r="M8" s="4">
+        <v>4</v>
+      </c>
+      <c r="N8" s="4">
+        <v>3</v>
+      </c>
+      <c r="O8" s="4">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>5</v>
+      </c>
+      <c r="R8" s="4">
+        <v>2</v>
+      </c>
+      <c r="S8" s="4">
+        <v>5</v>
+      </c>
+      <c r="T8" s="4">
+        <v>5</v>
+      </c>
+      <c r="U8" s="4">
+        <v>3</v>
+      </c>
+      <c r="V8" s="4">
+        <v>3</v>
+      </c>
+      <c r="W8" s="4">
+        <v>4</v>
+      </c>
+      <c r="X8" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>910454214</v>
       </c>
@@ -999,7 +1612,7 @@
       <c r="D9">
         <v>850644378</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>43199</v>
       </c>
       <c r="F9" t="s">
@@ -1008,8 +1621,74 @@
       <c r="G9" t="s">
         <v>98</v>
       </c>
+      <c r="H9" s="4">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4">
+        <v>7</v>
+      </c>
+      <c r="K9" s="4">
+        <v>6</v>
+      </c>
+      <c r="L9" s="4">
+        <v>6</v>
+      </c>
+      <c r="M9" s="4">
+        <v>4</v>
+      </c>
+      <c r="N9" s="4">
+        <v>4</v>
+      </c>
+      <c r="O9" s="4">
+        <v>2</v>
+      </c>
+      <c r="P9" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>4</v>
+      </c>
+      <c r="R9" s="4">
+        <v>3</v>
+      </c>
+      <c r="S9" s="4">
+        <v>5</v>
+      </c>
+      <c r="T9" s="4">
+        <v>5</v>
+      </c>
+      <c r="U9" s="4">
+        <v>3</v>
+      </c>
+      <c r="V9" s="4">
+        <v>3</v>
+      </c>
+      <c r="W9" s="4">
+        <v>4</v>
+      </c>
+      <c r="X9" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>913216859</v>
       </c>
@@ -1022,7 +1701,7 @@
       <c r="D10">
         <v>850644378</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>36900</v>
       </c>
       <c r="F10" t="s">
@@ -1031,8 +1710,74 @@
       <c r="G10" t="s">
         <v>99</v>
       </c>
+      <c r="H10" s="4">
+        <v>4</v>
+      </c>
+      <c r="I10" s="4">
+        <v>6</v>
+      </c>
+      <c r="J10" s="4">
+        <v>7</v>
+      </c>
+      <c r="K10" s="4">
+        <v>6</v>
+      </c>
+      <c r="L10" s="4">
+        <v>6</v>
+      </c>
+      <c r="M10" s="4">
+        <v>4</v>
+      </c>
+      <c r="N10" s="4">
+        <v>4</v>
+      </c>
+      <c r="O10" s="4">
+        <v>2</v>
+      </c>
+      <c r="P10" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>4</v>
+      </c>
+      <c r="R10" s="4">
+        <v>3</v>
+      </c>
+      <c r="S10" s="4">
+        <v>5</v>
+      </c>
+      <c r="T10" s="4">
+        <v>5</v>
+      </c>
+      <c r="U10" s="4">
+        <v>3</v>
+      </c>
+      <c r="V10" s="4">
+        <v>3</v>
+      </c>
+      <c r="W10" s="4">
+        <v>4</v>
+      </c>
+      <c r="X10" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>406359927</v>
       </c>
@@ -1045,7 +1790,7 @@
       <c r="D11">
         <v>850644378</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>45572</v>
       </c>
       <c r="F11" t="s">
@@ -1054,8 +1799,74 @@
       <c r="G11" t="s">
         <v>98</v>
       </c>
+      <c r="H11" s="4">
+        <v>4</v>
+      </c>
+      <c r="I11" s="4">
+        <v>5</v>
+      </c>
+      <c r="J11" s="4">
+        <v>6</v>
+      </c>
+      <c r="K11" s="4">
+        <v>5</v>
+      </c>
+      <c r="L11" s="4">
+        <v>6</v>
+      </c>
+      <c r="M11" s="4">
+        <v>4</v>
+      </c>
+      <c r="N11" s="4">
+        <v>4</v>
+      </c>
+      <c r="O11" s="4">
+        <v>2</v>
+      </c>
+      <c r="P11" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>4</v>
+      </c>
+      <c r="R11" s="4">
+        <v>3</v>
+      </c>
+      <c r="S11" s="4">
+        <v>5</v>
+      </c>
+      <c r="T11" s="4">
+        <v>4</v>
+      </c>
+      <c r="U11" s="4">
+        <v>3</v>
+      </c>
+      <c r="V11" s="4">
+        <v>3</v>
+      </c>
+      <c r="W11" s="4">
+        <v>3</v>
+      </c>
+      <c r="X11" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>977865948</v>
       </c>
@@ -1068,7 +1879,7 @@
       <c r="D12">
         <v>850644378</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>35319</v>
       </c>
       <c r="F12" t="s">
@@ -1077,8 +1888,74 @@
       <c r="G12" t="s">
         <v>98</v>
       </c>
+      <c r="H12" s="4">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4">
+        <v>6</v>
+      </c>
+      <c r="J12" s="4">
+        <v>7</v>
+      </c>
+      <c r="K12" s="4">
+        <v>6</v>
+      </c>
+      <c r="L12" s="4">
+        <v>6</v>
+      </c>
+      <c r="M12" s="4">
+        <v>4</v>
+      </c>
+      <c r="N12" s="4">
+        <v>4</v>
+      </c>
+      <c r="O12" s="4">
+        <v>2</v>
+      </c>
+      <c r="P12" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>4</v>
+      </c>
+      <c r="R12" s="4">
+        <v>3</v>
+      </c>
+      <c r="S12" s="4">
+        <v>5</v>
+      </c>
+      <c r="T12" s="4">
+        <v>4</v>
+      </c>
+      <c r="U12" s="4">
+        <v>3</v>
+      </c>
+      <c r="V12" s="4">
+        <v>3</v>
+      </c>
+      <c r="W12" s="4">
+        <v>3</v>
+      </c>
+      <c r="X12" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>401825245</v>
       </c>
@@ -1091,7 +1968,7 @@
       <c r="D13">
         <v>850644378</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F13" t="s">
@@ -1100,8 +1977,74 @@
       <c r="G13" t="s">
         <v>99</v>
       </c>
+      <c r="H13" s="4">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4">
+        <v>6</v>
+      </c>
+      <c r="J13" s="4">
+        <v>7</v>
+      </c>
+      <c r="K13" s="4">
+        <v>6</v>
+      </c>
+      <c r="L13" s="4">
+        <v>5</v>
+      </c>
+      <c r="M13" s="4">
+        <v>4</v>
+      </c>
+      <c r="N13" s="4">
+        <v>4</v>
+      </c>
+      <c r="O13" s="4">
+        <v>2</v>
+      </c>
+      <c r="P13" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>5</v>
+      </c>
+      <c r="R13" s="4">
+        <v>2</v>
+      </c>
+      <c r="S13" s="4">
+        <v>4</v>
+      </c>
+      <c r="T13" s="4">
+        <v>5</v>
+      </c>
+      <c r="U13" s="4">
+        <v>3</v>
+      </c>
+      <c r="V13" s="4">
+        <v>3</v>
+      </c>
+      <c r="W13" s="4">
+        <v>4</v>
+      </c>
+      <c r="X13" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>853276004</v>
       </c>
@@ -1114,7 +2057,7 @@
       <c r="D14">
         <v>850644378</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F14" t="s">
@@ -1123,8 +2066,74 @@
       <c r="G14" t="s">
         <v>99</v>
       </c>
+      <c r="H14" s="4">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>6</v>
+      </c>
+      <c r="L14" s="4">
+        <v>6</v>
+      </c>
+      <c r="M14" s="4">
+        <v>4</v>
+      </c>
+      <c r="N14" s="4">
+        <v>4</v>
+      </c>
+      <c r="O14" s="4">
+        <v>2</v>
+      </c>
+      <c r="P14" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>3</v>
+      </c>
+      <c r="R14" s="4">
+        <v>3</v>
+      </c>
+      <c r="S14" s="4">
+        <v>5</v>
+      </c>
+      <c r="T14" s="4">
+        <v>5</v>
+      </c>
+      <c r="U14" s="4">
+        <v>3</v>
+      </c>
+      <c r="V14" s="4">
+        <v>3</v>
+      </c>
+      <c r="W14" s="4">
+        <v>4</v>
+      </c>
+      <c r="X14" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>913202164</v>
       </c>
@@ -1137,7 +2146,7 @@
       <c r="D15">
         <v>850644378</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>41551</v>
       </c>
       <c r="F15" t="s">
@@ -1146,8 +2155,74 @@
       <c r="G15" t="s">
         <v>98</v>
       </c>
+      <c r="H15" s="4">
+        <v>4</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>6</v>
+      </c>
+      <c r="L15" s="4">
+        <v>6</v>
+      </c>
+      <c r="M15" s="4">
+        <v>4</v>
+      </c>
+      <c r="N15" s="4">
+        <v>4</v>
+      </c>
+      <c r="O15" s="4">
+        <v>2</v>
+      </c>
+      <c r="P15" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>5</v>
+      </c>
+      <c r="R15" s="4">
+        <v>3</v>
+      </c>
+      <c r="S15" s="4">
+        <v>5</v>
+      </c>
+      <c r="T15" s="4">
+        <v>5</v>
+      </c>
+      <c r="U15" s="4">
+        <v>3</v>
+      </c>
+      <c r="V15" s="4">
+        <v>3</v>
+      </c>
+      <c r="W15" s="4">
+        <v>4</v>
+      </c>
+      <c r="X15" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>945665354</v>
       </c>
@@ -1160,7 +2235,7 @@
       <c r="D16">
         <v>850644378</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
@@ -1169,8 +2244,74 @@
       <c r="G16" t="s">
         <v>97</v>
       </c>
+      <c r="H16" s="4">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>6</v>
+      </c>
+      <c r="L16" s="4">
+        <v>6</v>
+      </c>
+      <c r="M16" s="4">
+        <v>4</v>
+      </c>
+      <c r="N16" s="4">
+        <v>4</v>
+      </c>
+      <c r="O16" s="4">
+        <v>2</v>
+      </c>
+      <c r="P16" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>5</v>
+      </c>
+      <c r="R16" s="4">
+        <v>3</v>
+      </c>
+      <c r="S16" s="4">
+        <v>5</v>
+      </c>
+      <c r="T16" s="4">
+        <v>5</v>
+      </c>
+      <c r="U16" s="4">
+        <v>3</v>
+      </c>
+      <c r="V16" s="4">
+        <v>3</v>
+      </c>
+      <c r="W16" s="4">
+        <v>4</v>
+      </c>
+      <c r="X16" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>859709644</v>
       </c>
@@ -1183,7 +2324,7 @@
       <c r="D17">
         <v>850644378</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
@@ -1192,8 +2333,74 @@
       <c r="G17" t="s">
         <v>99</v>
       </c>
+      <c r="H17" s="4">
+        <v>4</v>
+      </c>
+      <c r="I17" s="4">
+        <v>4</v>
+      </c>
+      <c r="J17" s="4">
+        <v>6</v>
+      </c>
+      <c r="K17" s="4">
+        <v>6</v>
+      </c>
+      <c r="L17" s="4">
+        <v>5</v>
+      </c>
+      <c r="M17" s="4">
+        <v>3</v>
+      </c>
+      <c r="N17" s="4">
+        <v>4</v>
+      </c>
+      <c r="O17" s="4">
+        <v>2</v>
+      </c>
+      <c r="P17" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>4</v>
+      </c>
+      <c r="R17" s="4">
+        <v>3</v>
+      </c>
+      <c r="S17" s="4">
+        <v>6</v>
+      </c>
+      <c r="T17" s="4">
+        <v>5</v>
+      </c>
+      <c r="U17" s="4">
+        <v>3</v>
+      </c>
+      <c r="V17" s="4">
+        <v>3</v>
+      </c>
+      <c r="W17" s="4">
+        <v>4</v>
+      </c>
+      <c r="X17" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>939383568</v>
       </c>
@@ -1206,7 +2413,7 @@
       <c r="D18">
         <v>850644378</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
         <v>40910</v>
       </c>
       <c r="F18" t="s">
@@ -1215,8 +2422,74 @@
       <c r="G18" t="s">
         <v>98</v>
       </c>
+      <c r="H18" s="4">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4">
+        <v>6</v>
+      </c>
+      <c r="J18" s="4">
+        <v>7</v>
+      </c>
+      <c r="K18" s="4">
+        <v>6</v>
+      </c>
+      <c r="L18" s="4">
+        <v>5</v>
+      </c>
+      <c r="M18" s="4">
+        <v>4</v>
+      </c>
+      <c r="N18" s="4">
+        <v>4</v>
+      </c>
+      <c r="O18" s="4">
+        <v>2</v>
+      </c>
+      <c r="P18" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>4</v>
+      </c>
+      <c r="R18" s="4">
+        <v>3</v>
+      </c>
+      <c r="S18" s="4">
+        <v>5</v>
+      </c>
+      <c r="T18" s="4">
+        <v>4</v>
+      </c>
+      <c r="U18" s="4">
+        <v>1</v>
+      </c>
+      <c r="V18" s="4">
+        <v>3</v>
+      </c>
+      <c r="W18" s="4">
+        <v>4</v>
+      </c>
+      <c r="X18" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>853040657</v>
       </c>
@@ -1229,8 +2502,8 @@
       <c r="D19">
         <v>850644378</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>121</v>
+      <c r="E19" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="F19" t="s">
         <v>94</v>
@@ -1238,8 +2511,74 @@
       <c r="G19" t="s">
         <v>98</v>
       </c>
+      <c r="H19" s="4">
+        <v>4</v>
+      </c>
+      <c r="I19" s="4">
+        <v>6</v>
+      </c>
+      <c r="J19" s="4">
+        <v>6</v>
+      </c>
+      <c r="K19" s="4">
+        <v>6</v>
+      </c>
+      <c r="L19" s="4">
+        <v>6</v>
+      </c>
+      <c r="M19" s="4">
+        <v>4</v>
+      </c>
+      <c r="N19" s="4">
+        <v>4</v>
+      </c>
+      <c r="O19" s="4">
+        <v>2</v>
+      </c>
+      <c r="P19" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>5</v>
+      </c>
+      <c r="R19" s="4">
+        <v>3</v>
+      </c>
+      <c r="S19" s="4">
+        <v>5</v>
+      </c>
+      <c r="T19" s="4">
+        <v>6</v>
+      </c>
+      <c r="U19" s="4">
+        <v>3</v>
+      </c>
+      <c r="V19" s="4">
+        <v>3</v>
+      </c>
+      <c r="W19" s="4">
+        <v>3</v>
+      </c>
+      <c r="X19" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>973110670</v>
       </c>
@@ -1252,7 +2591,7 @@
       <c r="D20">
         <v>850644378</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>39939</v>
       </c>
       <c r="F20" t="s">
@@ -1261,8 +2600,74 @@
       <c r="G20" t="s">
         <v>100</v>
       </c>
+      <c r="H20" s="4">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4">
+        <v>6</v>
+      </c>
+      <c r="J20" s="4">
+        <v>7</v>
+      </c>
+      <c r="K20" s="4">
+        <v>6</v>
+      </c>
+      <c r="L20" s="4">
+        <v>6</v>
+      </c>
+      <c r="M20" s="4">
+        <v>4</v>
+      </c>
+      <c r="N20" s="4">
+        <v>4</v>
+      </c>
+      <c r="O20" s="4">
+        <v>2</v>
+      </c>
+      <c r="P20" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>5</v>
+      </c>
+      <c r="R20" s="4">
+        <v>3</v>
+      </c>
+      <c r="S20" s="4">
+        <v>5</v>
+      </c>
+      <c r="T20" s="4">
+        <v>6</v>
+      </c>
+      <c r="U20" s="4">
+        <v>3</v>
+      </c>
+      <c r="V20" s="4">
+        <v>3</v>
+      </c>
+      <c r="W20" s="4">
+        <v>3</v>
+      </c>
+      <c r="X20" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>900064205</v>
       </c>
@@ -1275,7 +2680,7 @@
       <c r="D21">
         <v>850644378</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F21" t="s">
@@ -1284,8 +2689,74 @@
       <c r="G21" t="s">
         <v>99</v>
       </c>
+      <c r="H21" s="4">
+        <v>4</v>
+      </c>
+      <c r="I21" s="4">
+        <v>6</v>
+      </c>
+      <c r="J21" s="4">
+        <v>7</v>
+      </c>
+      <c r="K21" s="4">
+        <v>6</v>
+      </c>
+      <c r="L21" s="4">
+        <v>5</v>
+      </c>
+      <c r="M21" s="4">
+        <v>5</v>
+      </c>
+      <c r="N21" s="4">
+        <v>3</v>
+      </c>
+      <c r="O21" s="4">
+        <v>2</v>
+      </c>
+      <c r="P21" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>5</v>
+      </c>
+      <c r="R21" s="4">
+        <v>4</v>
+      </c>
+      <c r="S21" s="4">
+        <v>5</v>
+      </c>
+      <c r="T21" s="4">
+        <v>5</v>
+      </c>
+      <c r="U21" s="4">
+        <v>3</v>
+      </c>
+      <c r="V21" s="4">
+        <v>3</v>
+      </c>
+      <c r="W21" s="4">
+        <v>4</v>
+      </c>
+      <c r="X21" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB21" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>853572311</v>
       </c>
@@ -1298,7 +2769,7 @@
       <c r="D22">
         <v>850644378</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F22" t="s">
@@ -1307,8 +2778,74 @@
       <c r="G22" t="s">
         <v>100</v>
       </c>
+      <c r="H22" s="4">
+        <v>5</v>
+      </c>
+      <c r="I22" s="4">
+        <v>6</v>
+      </c>
+      <c r="J22" s="4">
+        <v>7</v>
+      </c>
+      <c r="K22" s="4">
+        <v>6</v>
+      </c>
+      <c r="L22" s="4">
+        <v>5</v>
+      </c>
+      <c r="M22" s="4">
+        <v>4</v>
+      </c>
+      <c r="N22" s="4">
+        <v>3</v>
+      </c>
+      <c r="O22" s="4">
+        <v>2</v>
+      </c>
+      <c r="P22" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>5</v>
+      </c>
+      <c r="R22" s="4">
+        <v>2</v>
+      </c>
+      <c r="S22" s="4">
+        <v>4</v>
+      </c>
+      <c r="T22" s="4">
+        <v>5</v>
+      </c>
+      <c r="U22" s="4">
+        <v>3</v>
+      </c>
+      <c r="V22" s="4">
+        <v>3</v>
+      </c>
+      <c r="W22" s="4">
+        <v>4</v>
+      </c>
+      <c r="X22" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y22" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB22" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>403423981</v>
       </c>
@@ -1321,7 +2858,7 @@
       <c r="D23">
         <v>850644378</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F23" t="s">
@@ -1330,8 +2867,74 @@
       <c r="G23" t="s">
         <v>98</v>
       </c>
+      <c r="H23" s="4">
+        <v>4</v>
+      </c>
+      <c r="I23" s="4">
+        <v>5</v>
+      </c>
+      <c r="J23" s="4">
+        <v>7</v>
+      </c>
+      <c r="K23" s="4">
+        <v>6</v>
+      </c>
+      <c r="L23" s="4">
+        <v>5</v>
+      </c>
+      <c r="M23" s="4">
+        <v>3</v>
+      </c>
+      <c r="N23" s="4">
+        <v>2</v>
+      </c>
+      <c r="O23" s="4">
+        <v>2</v>
+      </c>
+      <c r="P23" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>5</v>
+      </c>
+      <c r="R23" s="4">
+        <v>2</v>
+      </c>
+      <c r="S23" s="4">
+        <v>5</v>
+      </c>
+      <c r="T23" s="4">
+        <v>4</v>
+      </c>
+      <c r="U23" s="4">
+        <v>2</v>
+      </c>
+      <c r="V23" s="4">
+        <v>3</v>
+      </c>
+      <c r="W23" s="4">
+        <v>4</v>
+      </c>
+      <c r="X23" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y23" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z23" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB23" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>406474395</v>
       </c>
@@ -1344,7 +2947,7 @@
       <c r="D24">
         <v>850644378</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <v>43991</v>
       </c>
       <c r="F24" t="s">
@@ -1353,8 +2956,74 @@
       <c r="G24" t="s">
         <v>97</v>
       </c>
+      <c r="H24" s="4">
+        <v>5</v>
+      </c>
+      <c r="I24" s="4">
+        <v>6</v>
+      </c>
+      <c r="J24" s="4">
+        <v>7</v>
+      </c>
+      <c r="K24" s="4">
+        <v>6</v>
+      </c>
+      <c r="L24" s="4">
+        <v>5</v>
+      </c>
+      <c r="M24" s="4">
+        <v>4</v>
+      </c>
+      <c r="N24" s="4">
+        <v>3</v>
+      </c>
+      <c r="O24" s="4">
+        <v>2</v>
+      </c>
+      <c r="P24" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>5</v>
+      </c>
+      <c r="R24" s="4">
+        <v>2</v>
+      </c>
+      <c r="S24" s="4">
+        <v>4</v>
+      </c>
+      <c r="T24" s="4">
+        <v>5</v>
+      </c>
+      <c r="U24" s="4">
+        <v>3</v>
+      </c>
+      <c r="V24" s="4">
+        <v>3</v>
+      </c>
+      <c r="W24" s="4">
+        <v>4</v>
+      </c>
+      <c r="X24" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y24" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB24" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>410698427</v>
       </c>
@@ -1367,7 +3036,7 @@
       <c r="D25">
         <v>850644378</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>39700</v>
       </c>
       <c r="F25" t="s">
@@ -1376,8 +3045,74 @@
       <c r="G25" t="s">
         <v>97</v>
       </c>
+      <c r="H25" s="4">
+        <v>4</v>
+      </c>
+      <c r="I25" s="4">
+        <v>4</v>
+      </c>
+      <c r="J25" s="4">
+        <v>7</v>
+      </c>
+      <c r="K25" s="4">
+        <v>6</v>
+      </c>
+      <c r="L25" s="4">
+        <v>5</v>
+      </c>
+      <c r="M25" s="4">
+        <v>3</v>
+      </c>
+      <c r="N25" s="4">
+        <v>4</v>
+      </c>
+      <c r="O25" s="4">
+        <v>2</v>
+      </c>
+      <c r="P25" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>4</v>
+      </c>
+      <c r="R25" s="4">
+        <v>3</v>
+      </c>
+      <c r="S25" s="4">
+        <v>6</v>
+      </c>
+      <c r="T25" s="4">
+        <v>5</v>
+      </c>
+      <c r="U25" s="4">
+        <v>3</v>
+      </c>
+      <c r="V25" s="4">
+        <v>3</v>
+      </c>
+      <c r="W25" s="4">
+        <v>4</v>
+      </c>
+      <c r="X25" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y25" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z25" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB25" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>949567580</v>
       </c>
@@ -1390,7 +3125,7 @@
       <c r="D26">
         <v>850644378</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="3">
         <v>43322</v>
       </c>
       <c r="F26" t="s">
@@ -1399,8 +3134,74 @@
       <c r="G26" t="s">
         <v>97</v>
       </c>
+      <c r="H26" s="4">
+        <v>4</v>
+      </c>
+      <c r="I26" s="4">
+        <v>7</v>
+      </c>
+      <c r="J26" s="4">
+        <v>7</v>
+      </c>
+      <c r="K26" s="4">
+        <v>7</v>
+      </c>
+      <c r="L26" s="4">
+        <v>7</v>
+      </c>
+      <c r="M26" s="4">
+        <v>4</v>
+      </c>
+      <c r="N26" s="4">
+        <v>3</v>
+      </c>
+      <c r="O26" s="4">
+        <v>2</v>
+      </c>
+      <c r="P26" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>3</v>
+      </c>
+      <c r="R26" s="4">
+        <v>3</v>
+      </c>
+      <c r="S26" s="4">
+        <v>5</v>
+      </c>
+      <c r="T26" s="4">
+        <v>5</v>
+      </c>
+      <c r="U26" s="4">
+        <v>3</v>
+      </c>
+      <c r="V26" s="4">
+        <v>3</v>
+      </c>
+      <c r="W26" s="4">
+        <v>4</v>
+      </c>
+      <c r="X26" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB26" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>919094060</v>
       </c>
@@ -1413,7 +3214,7 @@
       <c r="D27">
         <v>850644378</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F27" t="s">
@@ -1422,8 +3223,74 @@
       <c r="G27" t="s">
         <v>97</v>
       </c>
+      <c r="H27" s="4">
+        <v>5</v>
+      </c>
+      <c r="I27" s="4">
+        <v>7</v>
+      </c>
+      <c r="J27" s="4">
+        <v>7</v>
+      </c>
+      <c r="K27" s="4">
+        <v>6</v>
+      </c>
+      <c r="L27" s="4">
+        <v>7</v>
+      </c>
+      <c r="M27" s="4">
+        <v>5</v>
+      </c>
+      <c r="N27" s="4">
+        <v>4</v>
+      </c>
+      <c r="O27" s="4">
+        <v>2</v>
+      </c>
+      <c r="P27" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>4</v>
+      </c>
+      <c r="R27" s="4">
+        <v>3</v>
+      </c>
+      <c r="S27" s="4">
+        <v>3</v>
+      </c>
+      <c r="T27" s="4">
+        <v>4</v>
+      </c>
+      <c r="U27" s="4">
+        <v>3</v>
+      </c>
+      <c r="V27" s="4">
+        <v>3</v>
+      </c>
+      <c r="W27" s="4">
+        <v>4</v>
+      </c>
+      <c r="X27" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y27" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB27" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>902442078</v>
       </c>
@@ -1436,7 +3303,7 @@
       <c r="D28">
         <v>850644378</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F28" t="s">
@@ -1445,8 +3312,74 @@
       <c r="G28" t="s">
         <v>97</v>
       </c>
+      <c r="H28" s="4">
+        <v>4</v>
+      </c>
+      <c r="I28" s="4">
+        <v>6</v>
+      </c>
+      <c r="J28" s="4">
+        <v>7</v>
+      </c>
+      <c r="K28" s="4">
+        <v>6</v>
+      </c>
+      <c r="L28" s="4">
+        <v>5</v>
+      </c>
+      <c r="M28" s="4">
+        <v>5</v>
+      </c>
+      <c r="N28" s="4">
+        <v>3</v>
+      </c>
+      <c r="O28" s="4">
+        <v>2</v>
+      </c>
+      <c r="P28" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>5</v>
+      </c>
+      <c r="R28" s="4">
+        <v>4</v>
+      </c>
+      <c r="S28" s="4">
+        <v>5</v>
+      </c>
+      <c r="T28" s="4">
+        <v>5</v>
+      </c>
+      <c r="U28" s="4">
+        <v>3</v>
+      </c>
+      <c r="V28" s="4">
+        <v>3</v>
+      </c>
+      <c r="W28" s="4">
+        <v>4</v>
+      </c>
+      <c r="X28" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y28" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z28" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB28" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>907586069</v>
       </c>
@@ -1459,7 +3392,7 @@
       <c r="D29">
         <v>850644378</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="3">
         <v>37630</v>
       </c>
       <c r="F29" t="s">
@@ -1468,8 +3401,74 @@
       <c r="G29" t="s">
         <v>97</v>
       </c>
+      <c r="H29" s="4">
+        <v>4</v>
+      </c>
+      <c r="I29" s="4">
+        <v>6</v>
+      </c>
+      <c r="J29" s="4">
+        <v>7</v>
+      </c>
+      <c r="K29" s="4">
+        <v>6</v>
+      </c>
+      <c r="L29" s="4">
+        <v>6</v>
+      </c>
+      <c r="M29" s="4">
+        <v>4</v>
+      </c>
+      <c r="N29" s="4">
+        <v>4</v>
+      </c>
+      <c r="O29" s="4">
+        <v>2</v>
+      </c>
+      <c r="P29" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>6</v>
+      </c>
+      <c r="R29" s="4">
+        <v>3</v>
+      </c>
+      <c r="S29" s="4">
+        <v>4</v>
+      </c>
+      <c r="T29" s="4">
+        <v>5</v>
+      </c>
+      <c r="U29" s="4">
+        <v>3</v>
+      </c>
+      <c r="V29" s="4">
+        <v>3</v>
+      </c>
+      <c r="W29" s="4">
+        <v>4</v>
+      </c>
+      <c r="X29" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z29" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB29" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>907942197</v>
       </c>
@@ -1482,7 +3481,7 @@
       <c r="D30">
         <v>850644378</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F30" t="s">
@@ -1491,8 +3490,74 @@
       <c r="G30" t="s">
         <v>98</v>
       </c>
+      <c r="H30" s="4">
+        <v>5</v>
+      </c>
+      <c r="I30" s="4">
+        <v>7</v>
+      </c>
+      <c r="J30" s="4">
+        <v>7</v>
+      </c>
+      <c r="K30" s="4">
+        <v>6</v>
+      </c>
+      <c r="L30" s="4">
+        <v>7</v>
+      </c>
+      <c r="M30" s="4">
+        <v>5</v>
+      </c>
+      <c r="N30" s="4">
+        <v>4</v>
+      </c>
+      <c r="O30" s="4">
+        <v>2</v>
+      </c>
+      <c r="P30" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>4</v>
+      </c>
+      <c r="R30" s="4">
+        <v>3</v>
+      </c>
+      <c r="S30" s="4">
+        <v>3</v>
+      </c>
+      <c r="T30" s="4">
+        <v>4</v>
+      </c>
+      <c r="U30" s="4">
+        <v>3</v>
+      </c>
+      <c r="V30" s="4">
+        <v>3</v>
+      </c>
+      <c r="W30" s="4">
+        <v>4</v>
+      </c>
+      <c r="X30" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z30" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB30" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>902389196</v>
       </c>
@@ -1505,7 +3570,7 @@
       <c r="D31">
         <v>850644378</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F31" t="s">
@@ -1514,11 +3579,74 @@
       <c r="G31" t="s">
         <v>97</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>104</v>
+      <c r="H31" s="4">
+        <v>5</v>
+      </c>
+      <c r="I31" s="4">
+        <v>7</v>
+      </c>
+      <c r="J31" s="4">
+        <v>7</v>
+      </c>
+      <c r="K31" s="4">
+        <v>6</v>
+      </c>
+      <c r="L31" s="4">
+        <v>7</v>
+      </c>
+      <c r="M31" s="4">
+        <v>5</v>
+      </c>
+      <c r="N31" s="4">
+        <v>4</v>
+      </c>
+      <c r="O31" s="4">
+        <v>2</v>
+      </c>
+      <c r="P31" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>4</v>
+      </c>
+      <c r="R31" s="4">
+        <v>3</v>
+      </c>
+      <c r="S31" s="4">
+        <v>3</v>
+      </c>
+      <c r="T31" s="4">
+        <v>4</v>
+      </c>
+      <c r="U31" s="4">
+        <v>3</v>
+      </c>
+      <c r="V31" s="4">
+        <v>3</v>
+      </c>
+      <c r="W31" s="4">
+        <v>4</v>
+      </c>
+      <c r="X31" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z31" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB31" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="4">
+        <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>941512303</v>
       </c>
@@ -1531,7 +3659,7 @@
       <c r="D32">
         <v>850644378</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>37689</v>
       </c>
       <c r="F32" t="s">
@@ -1540,8 +3668,74 @@
       <c r="G32" t="s">
         <v>98</v>
       </c>
+      <c r="H32" s="4">
+        <v>5</v>
+      </c>
+      <c r="I32" s="4">
+        <v>7</v>
+      </c>
+      <c r="J32" s="4">
+        <v>7</v>
+      </c>
+      <c r="K32" s="4">
+        <v>6</v>
+      </c>
+      <c r="L32" s="4">
+        <v>7</v>
+      </c>
+      <c r="M32" s="4">
+        <v>5</v>
+      </c>
+      <c r="N32" s="4">
+        <v>4</v>
+      </c>
+      <c r="O32" s="4">
+        <v>2</v>
+      </c>
+      <c r="P32" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>4</v>
+      </c>
+      <c r="R32" s="4">
+        <v>3</v>
+      </c>
+      <c r="S32" s="4">
+        <v>3</v>
+      </c>
+      <c r="T32" s="4">
+        <v>4</v>
+      </c>
+      <c r="U32" s="4">
+        <v>3</v>
+      </c>
+      <c r="V32" s="4">
+        <v>3</v>
+      </c>
+      <c r="W32" s="4">
+        <v>4</v>
+      </c>
+      <c r="X32" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y32" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB32" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>850202847</v>
       </c>
@@ -1554,7 +3748,7 @@
       <c r="D33">
         <v>850644378</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="3">
         <v>39122</v>
       </c>
       <c r="F33" t="s">
@@ -1563,8 +3757,74 @@
       <c r="G33" t="s">
         <v>98</v>
       </c>
+      <c r="H33" s="4">
+        <v>5</v>
+      </c>
+      <c r="I33" s="4">
+        <v>7</v>
+      </c>
+      <c r="J33" s="4">
+        <v>7</v>
+      </c>
+      <c r="K33" s="4">
+        <v>6</v>
+      </c>
+      <c r="L33" s="4">
+        <v>7</v>
+      </c>
+      <c r="M33" s="4">
+        <v>5</v>
+      </c>
+      <c r="N33" s="4">
+        <v>4</v>
+      </c>
+      <c r="O33" s="4">
+        <v>2</v>
+      </c>
+      <c r="P33" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>4</v>
+      </c>
+      <c r="R33" s="4">
+        <v>3</v>
+      </c>
+      <c r="S33" s="4">
+        <v>3</v>
+      </c>
+      <c r="T33" s="4">
+        <v>4</v>
+      </c>
+      <c r="U33" s="4">
+        <v>3</v>
+      </c>
+      <c r="V33" s="4">
+        <v>3</v>
+      </c>
+      <c r="W33" s="4">
+        <v>4</v>
+      </c>
+      <c r="X33" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y33" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB33" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>904969409</v>
       </c>
@@ -1577,7 +3837,7 @@
       <c r="D34">
         <v>850644378</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="3">
         <v>40278</v>
       </c>
       <c r="F34" t="s">
@@ -1586,8 +3846,74 @@
       <c r="G34" t="s">
         <v>101</v>
       </c>
+      <c r="H34" s="4">
+        <v>4</v>
+      </c>
+      <c r="I34" s="4">
+        <v>6</v>
+      </c>
+      <c r="J34" s="4">
+        <v>7</v>
+      </c>
+      <c r="K34" s="4">
+        <v>6</v>
+      </c>
+      <c r="L34" s="4">
+        <v>6</v>
+      </c>
+      <c r="M34" s="4">
+        <v>4</v>
+      </c>
+      <c r="N34" s="4">
+        <v>4</v>
+      </c>
+      <c r="O34" s="4">
+        <v>2</v>
+      </c>
+      <c r="P34" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>6</v>
+      </c>
+      <c r="R34" s="4">
+        <v>3</v>
+      </c>
+      <c r="S34" s="4">
+        <v>4</v>
+      </c>
+      <c r="T34" s="4">
+        <v>5</v>
+      </c>
+      <c r="U34" s="4">
+        <v>3</v>
+      </c>
+      <c r="V34" s="4">
+        <v>3</v>
+      </c>
+      <c r="W34" s="4">
+        <v>4</v>
+      </c>
+      <c r="X34" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y34" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>911686699</v>
       </c>
@@ -1600,7 +3926,7 @@
       <c r="D35">
         <v>850644378</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F35" t="s">
@@ -1609,8 +3935,74 @@
       <c r="G35" t="s">
         <v>98</v>
       </c>
+      <c r="H35" s="4">
+        <v>4</v>
+      </c>
+      <c r="I35" s="4">
+        <v>4</v>
+      </c>
+      <c r="J35" s="4">
+        <v>6</v>
+      </c>
+      <c r="K35" s="4">
+        <v>6</v>
+      </c>
+      <c r="L35" s="4">
+        <v>6</v>
+      </c>
+      <c r="M35" s="4">
+        <v>4</v>
+      </c>
+      <c r="N35" s="4">
+        <v>4</v>
+      </c>
+      <c r="O35" s="4">
+        <v>2</v>
+      </c>
+      <c r="P35" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>4</v>
+      </c>
+      <c r="R35" s="4">
+        <v>3</v>
+      </c>
+      <c r="S35" s="4">
+        <v>5</v>
+      </c>
+      <c r="T35" s="4">
+        <v>5</v>
+      </c>
+      <c r="U35" s="4">
+        <v>3</v>
+      </c>
+      <c r="V35" s="4">
+        <v>3</v>
+      </c>
+      <c r="W35" s="4">
+        <v>4</v>
+      </c>
+      <c r="X35" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB35" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>984961466</v>
       </c>
@@ -1623,7 +4015,7 @@
       <c r="D36">
         <v>850644378</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="3">
         <v>39395</v>
       </c>
       <c r="F36" t="s">
@@ -1632,8 +4024,74 @@
       <c r="G36" t="s">
         <v>98</v>
       </c>
+      <c r="H36" s="4">
+        <v>4</v>
+      </c>
+      <c r="I36" s="4">
+        <v>6</v>
+      </c>
+      <c r="J36" s="4">
+        <v>6</v>
+      </c>
+      <c r="K36" s="4">
+        <v>6</v>
+      </c>
+      <c r="L36" s="4">
+        <v>6</v>
+      </c>
+      <c r="M36" s="4">
+        <v>4</v>
+      </c>
+      <c r="N36" s="4">
+        <v>3</v>
+      </c>
+      <c r="O36" s="4">
+        <v>2</v>
+      </c>
+      <c r="P36" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>5</v>
+      </c>
+      <c r="R36" s="4">
+        <v>3</v>
+      </c>
+      <c r="S36" s="4">
+        <v>5</v>
+      </c>
+      <c r="T36" s="4">
+        <v>6</v>
+      </c>
+      <c r="U36" s="4">
+        <v>3</v>
+      </c>
+      <c r="V36" s="4">
+        <v>3</v>
+      </c>
+      <c r="W36" s="4">
+        <v>4</v>
+      </c>
+      <c r="X36" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y36" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z36" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB36" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>852302116</v>
       </c>
@@ -1646,7 +4104,7 @@
       <c r="D37">
         <v>850644378</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="3">
         <v>40065</v>
       </c>
       <c r="F37" t="s">
@@ -1655,8 +4113,74 @@
       <c r="G37" t="s">
         <v>98</v>
       </c>
+      <c r="H37" s="4">
+        <v>4</v>
+      </c>
+      <c r="I37" s="4">
+        <v>7</v>
+      </c>
+      <c r="J37" s="4">
+        <v>7</v>
+      </c>
+      <c r="K37" s="4">
+        <v>7</v>
+      </c>
+      <c r="L37" s="4">
+        <v>7</v>
+      </c>
+      <c r="M37" s="4">
+        <v>4</v>
+      </c>
+      <c r="N37" s="4">
+        <v>3</v>
+      </c>
+      <c r="O37" s="4">
+        <v>2</v>
+      </c>
+      <c r="P37" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>3</v>
+      </c>
+      <c r="R37" s="4">
+        <v>3</v>
+      </c>
+      <c r="S37" s="4">
+        <v>5</v>
+      </c>
+      <c r="T37" s="4">
+        <v>5</v>
+      </c>
+      <c r="U37" s="4">
+        <v>3</v>
+      </c>
+      <c r="V37" s="4">
+        <v>3</v>
+      </c>
+      <c r="W37" s="4">
+        <v>4</v>
+      </c>
+      <c r="X37" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y37" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB37" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>904994597</v>
       </c>
@@ -1669,8 +4193,8 @@
       <c r="D38">
         <v>850644378</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>105</v>
+      <c r="E38" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="F38" t="s">
         <v>94</v>
@@ -1678,8 +4202,74 @@
       <c r="G38" t="s">
         <v>98</v>
       </c>
+      <c r="H38" s="4">
+        <v>4</v>
+      </c>
+      <c r="I38" s="4">
+        <v>6</v>
+      </c>
+      <c r="J38" s="4">
+        <v>7</v>
+      </c>
+      <c r="K38" s="4">
+        <v>6</v>
+      </c>
+      <c r="L38" s="4">
+        <v>6</v>
+      </c>
+      <c r="M38" s="4">
+        <v>4</v>
+      </c>
+      <c r="N38" s="4">
+        <v>4</v>
+      </c>
+      <c r="O38" s="4">
+        <v>2</v>
+      </c>
+      <c r="P38" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>6</v>
+      </c>
+      <c r="R38" s="4">
+        <v>3</v>
+      </c>
+      <c r="S38" s="4">
+        <v>5</v>
+      </c>
+      <c r="T38" s="4">
+        <v>5</v>
+      </c>
+      <c r="U38" s="4">
+        <v>3</v>
+      </c>
+      <c r="V38" s="4">
+        <v>3</v>
+      </c>
+      <c r="W38" s="4">
+        <v>4</v>
+      </c>
+      <c r="X38" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z38" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB38" s="4">
+        <v>2</v>
+      </c>
+      <c r="AC38" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>900122409</v>
       </c>
@@ -1692,7 +4282,7 @@
       <c r="D39">
         <v>850644378</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F39" t="s">
@@ -1701,8 +4291,74 @@
       <c r="G39" t="s">
         <v>97</v>
       </c>
+      <c r="H39" s="4">
+        <v>4</v>
+      </c>
+      <c r="I39" s="4">
+        <v>6</v>
+      </c>
+      <c r="J39" s="4">
+        <v>7</v>
+      </c>
+      <c r="K39" s="4">
+        <v>6</v>
+      </c>
+      <c r="L39" s="4">
+        <v>6</v>
+      </c>
+      <c r="M39" s="4">
+        <v>4</v>
+      </c>
+      <c r="N39" s="4">
+        <v>4</v>
+      </c>
+      <c r="O39" s="4">
+        <v>2</v>
+      </c>
+      <c r="P39" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>6</v>
+      </c>
+      <c r="R39" s="4">
+        <v>3</v>
+      </c>
+      <c r="S39" s="4">
+        <v>5</v>
+      </c>
+      <c r="T39" s="4">
+        <v>5</v>
+      </c>
+      <c r="U39" s="4">
+        <v>3</v>
+      </c>
+      <c r="V39" s="4">
+        <v>3</v>
+      </c>
+      <c r="W39" s="4">
+        <v>4</v>
+      </c>
+      <c r="X39" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y39" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z39" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB39" s="4">
+        <v>2</v>
+      </c>
+      <c r="AC39" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>953107901</v>
       </c>
@@ -1715,7 +4371,7 @@
       <c r="D40">
         <v>850644378</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="3">
         <v>37233</v>
       </c>
       <c r="F40" t="s">
@@ -1724,8 +4380,74 @@
       <c r="G40" t="s">
         <v>98</v>
       </c>
+      <c r="H40" s="4">
+        <v>4</v>
+      </c>
+      <c r="I40" s="4">
+        <v>7</v>
+      </c>
+      <c r="J40" s="4">
+        <v>7</v>
+      </c>
+      <c r="K40" s="4">
+        <v>7</v>
+      </c>
+      <c r="L40" s="4">
+        <v>7</v>
+      </c>
+      <c r="M40" s="4">
+        <v>4</v>
+      </c>
+      <c r="N40" s="4">
+        <v>3</v>
+      </c>
+      <c r="O40" s="4">
+        <v>2</v>
+      </c>
+      <c r="P40" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>4</v>
+      </c>
+      <c r="R40" s="4">
+        <v>3</v>
+      </c>
+      <c r="S40" s="4">
+        <v>5</v>
+      </c>
+      <c r="T40" s="4">
+        <v>5</v>
+      </c>
+      <c r="U40" s="4">
+        <v>3</v>
+      </c>
+      <c r="V40" s="4">
+        <v>3</v>
+      </c>
+      <c r="W40" s="4">
+        <v>4</v>
+      </c>
+      <c r="X40" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y40" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>403826068</v>
       </c>
@@ -1738,7 +4460,7 @@
       <c r="D41">
         <v>850644378</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F41" t="s">
@@ -1747,8 +4469,74 @@
       <c r="G41" t="s">
         <v>98</v>
       </c>
+      <c r="H41" s="4">
+        <v>4</v>
+      </c>
+      <c r="I41" s="4">
+        <v>6</v>
+      </c>
+      <c r="J41" s="4">
+        <v>6</v>
+      </c>
+      <c r="K41" s="4">
+        <v>6</v>
+      </c>
+      <c r="L41" s="4">
+        <v>6</v>
+      </c>
+      <c r="M41" s="4">
+        <v>4</v>
+      </c>
+      <c r="N41" s="4">
+        <v>2</v>
+      </c>
+      <c r="O41" s="4">
+        <v>2</v>
+      </c>
+      <c r="P41" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>5</v>
+      </c>
+      <c r="R41" s="4">
+        <v>3</v>
+      </c>
+      <c r="S41" s="4">
+        <v>5</v>
+      </c>
+      <c r="T41" s="4">
+        <v>6</v>
+      </c>
+      <c r="U41" s="4">
+        <v>3</v>
+      </c>
+      <c r="V41" s="4">
+        <v>3</v>
+      </c>
+      <c r="W41" s="4">
+        <v>4</v>
+      </c>
+      <c r="X41" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB41" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>989552252</v>
       </c>
@@ -1761,7 +4549,7 @@
       <c r="D42">
         <v>850644378</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F42" t="s">
@@ -1770,8 +4558,74 @@
       <c r="G42" t="s">
         <v>98</v>
       </c>
+      <c r="H42" s="4">
+        <v>4</v>
+      </c>
+      <c r="I42" s="4">
+        <v>7</v>
+      </c>
+      <c r="J42" s="4">
+        <v>7</v>
+      </c>
+      <c r="K42" s="4">
+        <v>7</v>
+      </c>
+      <c r="L42" s="4">
+        <v>7</v>
+      </c>
+      <c r="M42" s="4">
+        <v>4</v>
+      </c>
+      <c r="N42" s="4">
+        <v>3</v>
+      </c>
+      <c r="O42" s="4">
+        <v>2</v>
+      </c>
+      <c r="P42" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>3</v>
+      </c>
+      <c r="R42" s="4">
+        <v>3</v>
+      </c>
+      <c r="S42" s="4">
+        <v>5</v>
+      </c>
+      <c r="T42" s="4">
+        <v>5</v>
+      </c>
+      <c r="U42" s="4">
+        <v>3</v>
+      </c>
+      <c r="V42" s="4">
+        <v>3</v>
+      </c>
+      <c r="W42" s="4">
+        <v>4</v>
+      </c>
+      <c r="X42" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y42" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>852192368</v>
       </c>
@@ -1784,7 +4638,7 @@
       <c r="D43">
         <v>850644378</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F43" t="s">
@@ -1793,8 +4647,74 @@
       <c r="G43" t="s">
         <v>98</v>
       </c>
+      <c r="H43" s="4">
+        <v>4</v>
+      </c>
+      <c r="I43" s="4">
+        <v>6</v>
+      </c>
+      <c r="J43" s="4">
+        <v>7</v>
+      </c>
+      <c r="K43" s="4">
+        <v>6</v>
+      </c>
+      <c r="L43" s="4">
+        <v>5</v>
+      </c>
+      <c r="M43" s="4">
+        <v>5</v>
+      </c>
+      <c r="N43" s="4">
+        <v>3</v>
+      </c>
+      <c r="O43" s="4">
+        <v>2</v>
+      </c>
+      <c r="P43" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>5</v>
+      </c>
+      <c r="R43" s="4">
+        <v>4</v>
+      </c>
+      <c r="S43" s="4">
+        <v>5</v>
+      </c>
+      <c r="T43" s="4">
+        <v>5</v>
+      </c>
+      <c r="U43" s="4">
+        <v>3</v>
+      </c>
+      <c r="V43" s="4">
+        <v>3</v>
+      </c>
+      <c r="W43" s="4">
+        <v>4</v>
+      </c>
+      <c r="X43" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB43" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>911683332</v>
       </c>
@@ -1807,7 +4727,7 @@
       <c r="D44">
         <v>850644378</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="3">
         <v>37996</v>
       </c>
       <c r="F44" t="s">
@@ -1816,8 +4736,74 @@
       <c r="G44" t="s">
         <v>98</v>
       </c>
+      <c r="H44" s="4">
+        <v>4</v>
+      </c>
+      <c r="I44" s="4">
+        <v>6</v>
+      </c>
+      <c r="J44" s="4">
+        <v>7</v>
+      </c>
+      <c r="K44" s="4">
+        <v>6</v>
+      </c>
+      <c r="L44" s="4">
+        <v>5</v>
+      </c>
+      <c r="M44" s="4">
+        <v>5</v>
+      </c>
+      <c r="N44" s="4">
+        <v>3</v>
+      </c>
+      <c r="O44" s="4">
+        <v>2</v>
+      </c>
+      <c r="P44" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>5</v>
+      </c>
+      <c r="R44" s="4">
+        <v>3</v>
+      </c>
+      <c r="S44" s="4">
+        <v>5</v>
+      </c>
+      <c r="T44" s="4">
+        <v>5</v>
+      </c>
+      <c r="U44" s="4">
+        <v>3</v>
+      </c>
+      <c r="V44" s="4">
+        <v>3</v>
+      </c>
+      <c r="W44" s="4">
+        <v>4</v>
+      </c>
+      <c r="X44" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z44" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB44" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>858970445</v>
       </c>
@@ -1830,8 +4816,8 @@
       <c r="D45">
         <v>850644378</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>106</v>
+      <c r="E45" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F45" t="s">
         <v>95</v>
@@ -1839,8 +4825,74 @@
       <c r="G45" t="s">
         <v>98</v>
       </c>
+      <c r="H45" s="4">
+        <v>4</v>
+      </c>
+      <c r="I45" s="4">
+        <v>5</v>
+      </c>
+      <c r="J45" s="4">
+        <v>7</v>
+      </c>
+      <c r="K45" s="4">
+        <v>6</v>
+      </c>
+      <c r="L45" s="4">
+        <v>5</v>
+      </c>
+      <c r="M45" s="4">
+        <v>3</v>
+      </c>
+      <c r="N45" s="4">
+        <v>2</v>
+      </c>
+      <c r="O45" s="4">
+        <v>2</v>
+      </c>
+      <c r="P45" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>5</v>
+      </c>
+      <c r="R45" s="4">
+        <v>2</v>
+      </c>
+      <c r="S45" s="4">
+        <v>5</v>
+      </c>
+      <c r="T45" s="4">
+        <v>4</v>
+      </c>
+      <c r="U45" s="4">
+        <v>2</v>
+      </c>
+      <c r="V45" s="4">
+        <v>3</v>
+      </c>
+      <c r="W45" s="4">
+        <v>4</v>
+      </c>
+      <c r="X45" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y45" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z45" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA45" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB45" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>994329175</v>
       </c>
@@ -1853,7 +4905,7 @@
       <c r="D46">
         <v>850644378</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="3">
         <v>39700</v>
       </c>
       <c r="F46" t="s">
@@ -1862,8 +4914,74 @@
       <c r="G46" t="s">
         <v>102</v>
       </c>
+      <c r="H46" s="4">
+        <v>4</v>
+      </c>
+      <c r="I46" s="4">
+        <v>6</v>
+      </c>
+      <c r="J46" s="4">
+        <v>7</v>
+      </c>
+      <c r="K46" s="4">
+        <v>6</v>
+      </c>
+      <c r="L46" s="4">
+        <v>6</v>
+      </c>
+      <c r="M46" s="4">
+        <v>4</v>
+      </c>
+      <c r="N46" s="4">
+        <v>4</v>
+      </c>
+      <c r="O46" s="4">
+        <v>3</v>
+      </c>
+      <c r="P46" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>6</v>
+      </c>
+      <c r="R46" s="4">
+        <v>3</v>
+      </c>
+      <c r="S46" s="4">
+        <v>5</v>
+      </c>
+      <c r="T46" s="4">
+        <v>5</v>
+      </c>
+      <c r="U46" s="4">
+        <v>2</v>
+      </c>
+      <c r="V46" s="4">
+        <v>3</v>
+      </c>
+      <c r="W46" s="4">
+        <v>4</v>
+      </c>
+      <c r="X46" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA46" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB46" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC46" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>954240850</v>
       </c>
@@ -1876,8 +4994,8 @@
       <c r="D47">
         <v>850644378</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>107</v>
+      <c r="E47" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="F47" t="s">
         <v>94</v>
@@ -1885,8 +5003,74 @@
       <c r="G47" t="s">
         <v>98</v>
       </c>
+      <c r="H47" s="4">
+        <v>4</v>
+      </c>
+      <c r="I47" s="4">
+        <v>6</v>
+      </c>
+      <c r="J47" s="4">
+        <v>7</v>
+      </c>
+      <c r="K47" s="4">
+        <v>5</v>
+      </c>
+      <c r="L47" s="4">
+        <v>5</v>
+      </c>
+      <c r="M47" s="4">
+        <v>4</v>
+      </c>
+      <c r="N47" s="4">
+        <v>4</v>
+      </c>
+      <c r="O47" s="4">
+        <v>2</v>
+      </c>
+      <c r="P47" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>5</v>
+      </c>
+      <c r="R47" s="4">
+        <v>3</v>
+      </c>
+      <c r="S47" s="4">
+        <v>5</v>
+      </c>
+      <c r="T47" s="4">
+        <v>5</v>
+      </c>
+      <c r="U47" s="4">
+        <v>3</v>
+      </c>
+      <c r="V47" s="4">
+        <v>3</v>
+      </c>
+      <c r="W47" s="4">
+        <v>4</v>
+      </c>
+      <c r="X47" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA47" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB47" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>401555594</v>
       </c>
@@ -1899,8 +5083,8 @@
       <c r="D48">
         <v>850644378</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>108</v>
+      <c r="E48" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="F48" t="s">
         <v>94</v>
@@ -1908,8 +5092,74 @@
       <c r="G48" t="s">
         <v>98</v>
       </c>
+      <c r="H48" s="4">
+        <v>4</v>
+      </c>
+      <c r="I48" s="4">
+        <v>6</v>
+      </c>
+      <c r="J48" s="4">
+        <v>7</v>
+      </c>
+      <c r="K48" s="4">
+        <v>6</v>
+      </c>
+      <c r="L48" s="4">
+        <v>6</v>
+      </c>
+      <c r="M48" s="4">
+        <v>5</v>
+      </c>
+      <c r="N48" s="4">
+        <v>4</v>
+      </c>
+      <c r="O48" s="4">
+        <v>2</v>
+      </c>
+      <c r="P48" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>4</v>
+      </c>
+      <c r="R48" s="4">
+        <v>3</v>
+      </c>
+      <c r="S48" s="4">
+        <v>4</v>
+      </c>
+      <c r="T48" s="4">
+        <v>5</v>
+      </c>
+      <c r="U48" s="4">
+        <v>2</v>
+      </c>
+      <c r="V48" s="4">
+        <v>3</v>
+      </c>
+      <c r="W48" s="4">
+        <v>3</v>
+      </c>
+      <c r="X48" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA48" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB48" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC48" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>907952691</v>
       </c>
@@ -1922,8 +5172,8 @@
       <c r="D49">
         <v>850644378</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>109</v>
+      <c r="E49" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="F49" t="s">
         <v>94</v>
@@ -1931,8 +5181,74 @@
       <c r="G49" t="s">
         <v>98</v>
       </c>
+      <c r="H49" s="4">
+        <v>4</v>
+      </c>
+      <c r="I49" s="4">
+        <v>6</v>
+      </c>
+      <c r="J49" s="4">
+        <v>7</v>
+      </c>
+      <c r="K49" s="4">
+        <v>6</v>
+      </c>
+      <c r="L49" s="4">
+        <v>6</v>
+      </c>
+      <c r="M49" s="4">
+        <v>5</v>
+      </c>
+      <c r="N49" s="4">
+        <v>4</v>
+      </c>
+      <c r="O49" s="4">
+        <v>2</v>
+      </c>
+      <c r="P49" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>4</v>
+      </c>
+      <c r="R49" s="4">
+        <v>3</v>
+      </c>
+      <c r="S49" s="4">
+        <v>5</v>
+      </c>
+      <c r="T49" s="4">
+        <v>5</v>
+      </c>
+      <c r="U49" s="4">
+        <v>2</v>
+      </c>
+      <c r="V49" s="4">
+        <v>3</v>
+      </c>
+      <c r="W49" s="4">
+        <v>3</v>
+      </c>
+      <c r="X49" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA49" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB49" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>402189757</v>
       </c>
@@ -1945,8 +5261,8 @@
       <c r="D50">
         <v>850644378</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>110</v>
+      <c r="E50" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="F50" t="s">
         <v>94</v>
@@ -1954,8 +5270,74 @@
       <c r="G50" t="s">
         <v>98</v>
       </c>
+      <c r="H50" s="4">
+        <v>4</v>
+      </c>
+      <c r="I50" s="4">
+        <v>6</v>
+      </c>
+      <c r="J50" s="4">
+        <v>6</v>
+      </c>
+      <c r="K50" s="4">
+        <v>6</v>
+      </c>
+      <c r="L50" s="4">
+        <v>6</v>
+      </c>
+      <c r="M50" s="4">
+        <v>4</v>
+      </c>
+      <c r="N50" s="4">
+        <v>3</v>
+      </c>
+      <c r="O50" s="4">
+        <v>2</v>
+      </c>
+      <c r="P50" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>5</v>
+      </c>
+      <c r="R50" s="4">
+        <v>3</v>
+      </c>
+      <c r="S50" s="4">
+        <v>5</v>
+      </c>
+      <c r="T50" s="4">
+        <v>6</v>
+      </c>
+      <c r="U50" s="4">
+        <v>3</v>
+      </c>
+      <c r="V50" s="4">
+        <v>3</v>
+      </c>
+      <c r="W50" s="4">
+        <v>4</v>
+      </c>
+      <c r="X50" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y50" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z50" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA50" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB50" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>912621182</v>
       </c>
@@ -1968,8 +5350,8 @@
       <c r="D51">
         <v>850644378</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>111</v>
+      <c r="E51" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F51" t="s">
         <v>94</v>
@@ -1977,8 +5359,74 @@
       <c r="G51" t="s">
         <v>98</v>
       </c>
+      <c r="H51" s="4">
+        <v>4</v>
+      </c>
+      <c r="I51" s="4">
+        <v>6</v>
+      </c>
+      <c r="J51" s="4">
+        <v>7</v>
+      </c>
+      <c r="K51" s="4">
+        <v>6</v>
+      </c>
+      <c r="L51" s="4">
+        <v>6</v>
+      </c>
+      <c r="M51" s="4">
+        <v>4</v>
+      </c>
+      <c r="N51" s="4">
+        <v>4</v>
+      </c>
+      <c r="O51" s="4">
+        <v>3</v>
+      </c>
+      <c r="P51" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>5</v>
+      </c>
+      <c r="R51" s="4">
+        <v>3</v>
+      </c>
+      <c r="S51" s="4">
+        <v>5</v>
+      </c>
+      <c r="T51" s="4">
+        <v>5</v>
+      </c>
+      <c r="U51" s="4">
+        <v>2</v>
+      </c>
+      <c r="V51" s="4">
+        <v>3</v>
+      </c>
+      <c r="W51" s="4">
+        <v>4</v>
+      </c>
+      <c r="X51" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y51" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z51" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA51" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB51" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>997950167</v>
       </c>
@@ -1991,8 +5439,8 @@
       <c r="D52">
         <v>850644378</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>112</v>
+      <c r="E52" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="F52" t="s">
         <v>94</v>
@@ -2000,8 +5448,74 @@
       <c r="G52" t="s">
         <v>102</v>
       </c>
+      <c r="H52" s="4">
+        <v>4</v>
+      </c>
+      <c r="I52" s="4">
+        <v>6</v>
+      </c>
+      <c r="J52" s="4">
+        <v>7</v>
+      </c>
+      <c r="K52" s="4">
+        <v>6</v>
+      </c>
+      <c r="L52" s="4">
+        <v>6</v>
+      </c>
+      <c r="M52" s="4">
+        <v>5</v>
+      </c>
+      <c r="N52" s="4">
+        <v>4</v>
+      </c>
+      <c r="O52" s="4">
+        <v>2</v>
+      </c>
+      <c r="P52" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>4</v>
+      </c>
+      <c r="R52" s="4">
+        <v>3</v>
+      </c>
+      <c r="S52" s="4">
+        <v>5</v>
+      </c>
+      <c r="T52" s="4">
+        <v>5</v>
+      </c>
+      <c r="U52" s="4">
+        <v>2</v>
+      </c>
+      <c r="V52" s="4">
+        <v>3</v>
+      </c>
+      <c r="W52" s="4">
+        <v>3</v>
+      </c>
+      <c r="X52" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA52" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB52" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC52" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>851544346</v>
       </c>
@@ -2014,7 +5528,7 @@
       <c r="D53">
         <v>850644378</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="3">
         <v>39974</v>
       </c>
       <c r="F53" t="s">
@@ -2023,8 +5537,74 @@
       <c r="G53" t="s">
         <v>98</v>
       </c>
+      <c r="H53" s="4">
+        <v>4</v>
+      </c>
+      <c r="I53" s="4">
+        <v>6</v>
+      </c>
+      <c r="J53" s="4">
+        <v>6</v>
+      </c>
+      <c r="K53" s="4">
+        <v>6</v>
+      </c>
+      <c r="L53" s="4">
+        <v>6</v>
+      </c>
+      <c r="M53" s="4">
+        <v>4</v>
+      </c>
+      <c r="N53" s="4">
+        <v>3</v>
+      </c>
+      <c r="O53" s="4">
+        <v>2</v>
+      </c>
+      <c r="P53" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>5</v>
+      </c>
+      <c r="R53" s="4">
+        <v>3</v>
+      </c>
+      <c r="S53" s="4">
+        <v>5</v>
+      </c>
+      <c r="T53" s="4">
+        <v>6</v>
+      </c>
+      <c r="U53" s="4">
+        <v>3</v>
+      </c>
+      <c r="V53" s="4">
+        <v>3</v>
+      </c>
+      <c r="W53" s="4">
+        <v>4</v>
+      </c>
+      <c r="X53" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y53" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z53" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB53" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC53" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>851723775</v>
       </c>
@@ -2037,7 +5617,7 @@
       <c r="D54">
         <v>850644378</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="3">
         <v>40888</v>
       </c>
       <c r="F54" t="s">
@@ -2046,8 +5626,74 @@
       <c r="G54" t="s">
         <v>98</v>
       </c>
+      <c r="H54" s="4">
+        <v>4</v>
+      </c>
+      <c r="I54" s="4">
+        <v>6</v>
+      </c>
+      <c r="J54" s="4">
+        <v>7</v>
+      </c>
+      <c r="K54" s="4">
+        <v>6</v>
+      </c>
+      <c r="L54" s="4">
+        <v>5</v>
+      </c>
+      <c r="M54" s="4">
+        <v>5</v>
+      </c>
+      <c r="N54" s="4">
+        <v>3</v>
+      </c>
+      <c r="O54" s="4">
+        <v>2</v>
+      </c>
+      <c r="P54" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>5</v>
+      </c>
+      <c r="R54" s="4">
+        <v>4</v>
+      </c>
+      <c r="S54" s="4">
+        <v>5</v>
+      </c>
+      <c r="T54" s="4">
+        <v>5</v>
+      </c>
+      <c r="U54" s="4">
+        <v>3</v>
+      </c>
+      <c r="V54" s="4">
+        <v>3</v>
+      </c>
+      <c r="W54" s="4">
+        <v>4</v>
+      </c>
+      <c r="X54" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB54" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>853977841</v>
       </c>
@@ -2060,8 +5706,8 @@
       <c r="D55">
         <v>850644378</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>113</v>
+      <c r="E55" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="F55" t="s">
         <v>94</v>
@@ -2069,8 +5715,74 @@
       <c r="G55" t="s">
         <v>98</v>
       </c>
+      <c r="H55" s="4">
+        <v>4</v>
+      </c>
+      <c r="I55" s="4">
+        <v>6</v>
+      </c>
+      <c r="J55" s="4">
+        <v>6</v>
+      </c>
+      <c r="K55" s="4">
+        <v>6</v>
+      </c>
+      <c r="L55" s="4">
+        <v>6</v>
+      </c>
+      <c r="M55" s="4">
+        <v>4</v>
+      </c>
+      <c r="N55" s="4">
+        <v>3</v>
+      </c>
+      <c r="O55" s="4">
+        <v>2</v>
+      </c>
+      <c r="P55" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>5</v>
+      </c>
+      <c r="R55" s="4">
+        <v>3</v>
+      </c>
+      <c r="S55" s="4">
+        <v>5</v>
+      </c>
+      <c r="T55" s="4">
+        <v>6</v>
+      </c>
+      <c r="U55" s="4">
+        <v>3</v>
+      </c>
+      <c r="V55" s="4">
+        <v>3</v>
+      </c>
+      <c r="W55" s="4">
+        <v>4</v>
+      </c>
+      <c r="X55" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y55" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z55" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB55" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>401012653</v>
       </c>
@@ -2083,7 +5795,7 @@
       <c r="D56">
         <v>850644378</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="3">
         <v>45544</v>
       </c>
       <c r="F56" t="s">
@@ -2092,8 +5804,74 @@
       <c r="G56" t="s">
         <v>98</v>
       </c>
+      <c r="H56" s="4">
+        <v>5</v>
+      </c>
+      <c r="I56" s="4">
+        <v>6</v>
+      </c>
+      <c r="J56" s="4">
+        <v>7</v>
+      </c>
+      <c r="K56" s="4">
+        <v>6</v>
+      </c>
+      <c r="L56" s="4">
+        <v>5</v>
+      </c>
+      <c r="M56" s="4">
+        <v>4</v>
+      </c>
+      <c r="N56" s="4">
+        <v>3</v>
+      </c>
+      <c r="O56" s="4">
+        <v>2</v>
+      </c>
+      <c r="P56" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q56" s="4">
+        <v>5</v>
+      </c>
+      <c r="R56" s="4">
+        <v>2</v>
+      </c>
+      <c r="S56" s="4">
+        <v>4</v>
+      </c>
+      <c r="T56" s="4">
+        <v>5</v>
+      </c>
+      <c r="U56" s="4">
+        <v>3</v>
+      </c>
+      <c r="V56" s="4">
+        <v>3</v>
+      </c>
+      <c r="W56" s="4">
+        <v>4</v>
+      </c>
+      <c r="X56" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y56" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z56" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB56" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>854879103</v>
       </c>
@@ -2106,7 +5884,7 @@
       <c r="D57">
         <v>850644378</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="3">
         <v>45690</v>
       </c>
       <c r="F57" t="s">
@@ -2115,8 +5893,74 @@
       <c r="G57" t="s">
         <v>98</v>
       </c>
+      <c r="H57" s="4">
+        <v>5</v>
+      </c>
+      <c r="I57" s="4">
+        <v>6</v>
+      </c>
+      <c r="J57" s="4">
+        <v>7</v>
+      </c>
+      <c r="K57" s="4">
+        <v>6</v>
+      </c>
+      <c r="L57" s="4">
+        <v>5</v>
+      </c>
+      <c r="M57" s="4">
+        <v>4</v>
+      </c>
+      <c r="N57" s="4">
+        <v>3</v>
+      </c>
+      <c r="O57" s="4">
+        <v>2</v>
+      </c>
+      <c r="P57" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="4">
+        <v>5</v>
+      </c>
+      <c r="R57" s="4">
+        <v>2</v>
+      </c>
+      <c r="S57" s="4">
+        <v>4</v>
+      </c>
+      <c r="T57" s="4">
+        <v>5</v>
+      </c>
+      <c r="U57" s="4">
+        <v>3</v>
+      </c>
+      <c r="V57" s="4">
+        <v>3</v>
+      </c>
+      <c r="W57" s="4">
+        <v>4</v>
+      </c>
+      <c r="X57" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y57" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB57" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>850379611</v>
       </c>
@@ -2129,8 +5973,8 @@
       <c r="D58">
         <v>850644378</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>114</v>
+      <c r="E58" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="F58" t="s">
         <v>94</v>
@@ -2138,8 +5982,74 @@
       <c r="G58" t="s">
         <v>97</v>
       </c>
+      <c r="H58" s="4">
+        <v>4</v>
+      </c>
+      <c r="I58" s="4">
+        <v>5</v>
+      </c>
+      <c r="J58" s="4">
+        <v>7</v>
+      </c>
+      <c r="K58" s="4">
+        <v>6</v>
+      </c>
+      <c r="L58" s="4">
+        <v>6</v>
+      </c>
+      <c r="M58" s="4">
+        <v>4</v>
+      </c>
+      <c r="N58" s="4">
+        <v>3</v>
+      </c>
+      <c r="O58" s="4">
+        <v>2</v>
+      </c>
+      <c r="P58" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="4">
+        <v>5</v>
+      </c>
+      <c r="R58" s="4">
+        <v>3</v>
+      </c>
+      <c r="S58" s="4">
+        <v>5</v>
+      </c>
+      <c r="T58" s="4">
+        <v>6</v>
+      </c>
+      <c r="U58" s="4">
+        <v>3</v>
+      </c>
+      <c r="V58" s="4">
+        <v>3</v>
+      </c>
+      <c r="W58" s="4">
+        <v>4</v>
+      </c>
+      <c r="X58" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB58" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>927702787</v>
       </c>
@@ -2152,8 +6062,8 @@
       <c r="D59">
         <v>850644378</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>115</v>
+      <c r="E59" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>94</v>
@@ -2161,8 +6071,74 @@
       <c r="G59" t="s">
         <v>97</v>
       </c>
+      <c r="H59" s="4">
+        <v>4</v>
+      </c>
+      <c r="I59" s="4">
+        <v>6</v>
+      </c>
+      <c r="J59" s="4">
+        <v>7</v>
+      </c>
+      <c r="K59" s="4">
+        <v>6</v>
+      </c>
+      <c r="L59" s="4">
+        <v>6</v>
+      </c>
+      <c r="M59" s="4">
+        <v>4</v>
+      </c>
+      <c r="N59" s="4">
+        <v>3</v>
+      </c>
+      <c r="O59" s="4">
+        <v>2</v>
+      </c>
+      <c r="P59" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="4">
+        <v>5</v>
+      </c>
+      <c r="R59" s="4">
+        <v>3</v>
+      </c>
+      <c r="S59" s="4">
+        <v>5</v>
+      </c>
+      <c r="T59" s="4">
+        <v>6</v>
+      </c>
+      <c r="U59" s="4">
+        <v>3</v>
+      </c>
+      <c r="V59" s="4">
+        <v>3</v>
+      </c>
+      <c r="W59" s="4">
+        <v>4</v>
+      </c>
+      <c r="X59" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB59" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>906832084</v>
       </c>
@@ -2175,7 +6151,7 @@
       <c r="D60">
         <v>850644378</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="3">
         <v>43384</v>
       </c>
       <c r="F60" t="s">
@@ -2184,8 +6160,74 @@
       <c r="G60" t="s">
         <v>98</v>
       </c>
+      <c r="H60" s="4">
+        <v>4</v>
+      </c>
+      <c r="I60" s="4">
+        <v>6</v>
+      </c>
+      <c r="J60" s="4">
+        <v>7</v>
+      </c>
+      <c r="K60" s="4">
+        <v>6</v>
+      </c>
+      <c r="L60" s="4">
+        <v>6</v>
+      </c>
+      <c r="M60" s="4">
+        <v>4</v>
+      </c>
+      <c r="N60" s="4">
+        <v>3</v>
+      </c>
+      <c r="O60" s="4">
+        <v>2</v>
+      </c>
+      <c r="P60" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>5</v>
+      </c>
+      <c r="R60" s="4">
+        <v>3</v>
+      </c>
+      <c r="S60" s="4">
+        <v>5</v>
+      </c>
+      <c r="T60" s="4">
+        <v>6</v>
+      </c>
+      <c r="U60" s="4">
+        <v>3</v>
+      </c>
+      <c r="V60" s="4">
+        <v>3</v>
+      </c>
+      <c r="W60" s="4">
+        <v>4</v>
+      </c>
+      <c r="X60" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA60" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB60" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>946826138</v>
       </c>
@@ -2198,8 +6240,8 @@
       <c r="D61">
         <v>850644378</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>116</v>
+      <c r="E61" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="F61" t="s">
         <v>94</v>
@@ -2207,8 +6249,74 @@
       <c r="G61" t="s">
         <v>97</v>
       </c>
+      <c r="H61" s="4">
+        <v>4</v>
+      </c>
+      <c r="I61" s="4">
+        <v>6</v>
+      </c>
+      <c r="J61" s="4">
+        <v>7</v>
+      </c>
+      <c r="K61" s="4">
+        <v>6</v>
+      </c>
+      <c r="L61" s="4">
+        <v>6</v>
+      </c>
+      <c r="M61" s="4">
+        <v>4</v>
+      </c>
+      <c r="N61" s="4">
+        <v>3</v>
+      </c>
+      <c r="O61" s="4">
+        <v>2</v>
+      </c>
+      <c r="P61" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>5</v>
+      </c>
+      <c r="R61" s="4">
+        <v>3</v>
+      </c>
+      <c r="S61" s="4">
+        <v>5</v>
+      </c>
+      <c r="T61" s="4">
+        <v>6</v>
+      </c>
+      <c r="U61" s="4">
+        <v>3</v>
+      </c>
+      <c r="V61" s="4">
+        <v>3</v>
+      </c>
+      <c r="W61" s="4">
+        <v>4</v>
+      </c>
+      <c r="X61" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y61" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z61" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA61" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB61" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC61" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>854136140</v>
       </c>
@@ -2221,8 +6329,8 @@
       <c r="D62">
         <v>850644378</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>117</v>
+      <c r="E62" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="F62" t="s">
         <v>94</v>
@@ -2230,8 +6338,74 @@
       <c r="G62" t="s">
         <v>97</v>
       </c>
+      <c r="H62" s="4">
+        <v>4</v>
+      </c>
+      <c r="I62" s="4">
+        <v>5</v>
+      </c>
+      <c r="J62" s="4">
+        <v>7</v>
+      </c>
+      <c r="K62" s="4">
+        <v>6</v>
+      </c>
+      <c r="L62" s="4">
+        <v>6</v>
+      </c>
+      <c r="M62" s="4">
+        <v>4</v>
+      </c>
+      <c r="N62" s="4">
+        <v>3</v>
+      </c>
+      <c r="O62" s="4">
+        <v>2</v>
+      </c>
+      <c r="P62" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>5</v>
+      </c>
+      <c r="R62" s="4">
+        <v>3</v>
+      </c>
+      <c r="S62" s="4">
+        <v>5</v>
+      </c>
+      <c r="T62" s="4">
+        <v>6</v>
+      </c>
+      <c r="U62" s="4">
+        <v>3</v>
+      </c>
+      <c r="V62" s="4">
+        <v>3</v>
+      </c>
+      <c r="W62" s="4">
+        <v>4</v>
+      </c>
+      <c r="X62" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB62" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC62" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>939380949</v>
       </c>
@@ -2244,8 +6418,8 @@
       <c r="D63">
         <v>850644378</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>118</v>
+      <c r="E63" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="F63" t="s">
         <v>94</v>
@@ -2253,8 +6427,74 @@
       <c r="G63" t="s">
         <v>97</v>
       </c>
+      <c r="H63" s="4">
+        <v>4</v>
+      </c>
+      <c r="I63" s="4">
+        <v>5</v>
+      </c>
+      <c r="J63" s="4">
+        <v>7</v>
+      </c>
+      <c r="K63" s="4">
+        <v>6</v>
+      </c>
+      <c r="L63" s="4">
+        <v>6</v>
+      </c>
+      <c r="M63" s="4">
+        <v>4</v>
+      </c>
+      <c r="N63" s="4">
+        <v>3</v>
+      </c>
+      <c r="O63" s="4">
+        <v>2</v>
+      </c>
+      <c r="P63" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>5</v>
+      </c>
+      <c r="R63" s="4">
+        <v>3</v>
+      </c>
+      <c r="S63" s="4">
+        <v>5</v>
+      </c>
+      <c r="T63" s="4">
+        <v>6</v>
+      </c>
+      <c r="U63" s="4">
+        <v>3</v>
+      </c>
+      <c r="V63" s="4">
+        <v>3</v>
+      </c>
+      <c r="W63" s="4">
+        <v>4</v>
+      </c>
+      <c r="X63" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y63" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z63" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB63" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>853214500</v>
       </c>
@@ -2267,7 +6507,7 @@
       <c r="D64">
         <v>850644378</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F64" t="s">
@@ -2276,8 +6516,74 @@
       <c r="G64" t="s">
         <v>97</v>
       </c>
+      <c r="H64" s="4">
+        <v>4</v>
+      </c>
+      <c r="I64" s="4">
+        <v>5</v>
+      </c>
+      <c r="J64" s="4">
+        <v>7</v>
+      </c>
+      <c r="K64" s="4">
+        <v>6</v>
+      </c>
+      <c r="L64" s="4">
+        <v>6</v>
+      </c>
+      <c r="M64" s="4">
+        <v>4</v>
+      </c>
+      <c r="N64" s="4">
+        <v>3</v>
+      </c>
+      <c r="O64" s="4">
+        <v>2</v>
+      </c>
+      <c r="P64" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>5</v>
+      </c>
+      <c r="R64" s="4">
+        <v>3</v>
+      </c>
+      <c r="S64" s="4">
+        <v>5</v>
+      </c>
+      <c r="T64" s="4">
+        <v>6</v>
+      </c>
+      <c r="U64" s="4">
+        <v>3</v>
+      </c>
+      <c r="V64" s="4">
+        <v>3</v>
+      </c>
+      <c r="W64" s="4">
+        <v>4</v>
+      </c>
+      <c r="X64" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y64" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z64" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB64" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>984961474</v>
       </c>
@@ -2290,8 +6596,8 @@
       <c r="D65">
         <v>850644378</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>119</v>
+      <c r="E65" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="F65" t="s">
         <v>95</v>
@@ -2299,8 +6605,74 @@
       <c r="G65" t="s">
         <v>98</v>
       </c>
+      <c r="H65" s="4">
+        <v>4</v>
+      </c>
+      <c r="I65" s="4">
+        <v>6</v>
+      </c>
+      <c r="J65" s="4">
+        <v>7</v>
+      </c>
+      <c r="K65" s="4">
+        <v>6</v>
+      </c>
+      <c r="L65" s="4">
+        <v>6</v>
+      </c>
+      <c r="M65" s="4">
+        <v>4</v>
+      </c>
+      <c r="N65" s="4">
+        <v>3</v>
+      </c>
+      <c r="O65" s="4">
+        <v>2</v>
+      </c>
+      <c r="P65" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>5</v>
+      </c>
+      <c r="R65" s="4">
+        <v>3</v>
+      </c>
+      <c r="S65" s="4">
+        <v>5</v>
+      </c>
+      <c r="T65" s="4">
+        <v>6</v>
+      </c>
+      <c r="U65" s="4">
+        <v>3</v>
+      </c>
+      <c r="V65" s="4">
+        <v>3</v>
+      </c>
+      <c r="W65" s="4">
+        <v>4</v>
+      </c>
+      <c r="X65" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y65" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z65" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB65" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC65" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>858609795</v>
       </c>
@@ -2313,7 +6685,7 @@
       <c r="D66">
         <v>850644378</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="3">
         <v>45536</v>
       </c>
       <c r="F66" t="s">
@@ -2322,8 +6694,74 @@
       <c r="G66" t="s">
         <v>103</v>
       </c>
+      <c r="H66" s="4">
+        <v>2</v>
+      </c>
+      <c r="I66" s="4">
+        <v>5</v>
+      </c>
+      <c r="J66" s="4">
+        <v>7</v>
+      </c>
+      <c r="K66" s="4">
+        <v>5</v>
+      </c>
+      <c r="L66" s="4">
+        <v>5</v>
+      </c>
+      <c r="M66" s="4">
+        <v>4</v>
+      </c>
+      <c r="N66" s="4">
+        <v>4</v>
+      </c>
+      <c r="O66" s="4">
+        <v>4</v>
+      </c>
+      <c r="P66" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>4</v>
+      </c>
+      <c r="R66" s="4">
+        <v>3</v>
+      </c>
+      <c r="S66" s="4">
+        <v>5</v>
+      </c>
+      <c r="T66" s="4">
+        <v>5</v>
+      </c>
+      <c r="U66" s="4">
+        <v>3</v>
+      </c>
+      <c r="V66" s="4">
+        <v>3</v>
+      </c>
+      <c r="W66" s="4">
+        <v>3</v>
+      </c>
+      <c r="X66" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB66" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>936853365</v>
       </c>
@@ -2336,7 +6774,7 @@
       <c r="D67">
         <v>850644378</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E67" s="3">
         <v>41910</v>
       </c>
       <c r="F67" t="s">
@@ -2345,8 +6783,74 @@
       <c r="G67" t="s">
         <v>98</v>
       </c>
+      <c r="H67" s="4">
+        <v>4</v>
+      </c>
+      <c r="I67" s="4">
+        <v>6</v>
+      </c>
+      <c r="J67" s="4">
+        <v>7</v>
+      </c>
+      <c r="K67" s="4">
+        <v>6</v>
+      </c>
+      <c r="L67" s="4">
+        <v>6</v>
+      </c>
+      <c r="M67" s="4">
+        <v>4</v>
+      </c>
+      <c r="N67" s="4">
+        <v>3</v>
+      </c>
+      <c r="O67" s="4">
+        <v>2</v>
+      </c>
+      <c r="P67" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>5</v>
+      </c>
+      <c r="R67" s="4">
+        <v>3</v>
+      </c>
+      <c r="S67" s="4">
+        <v>5</v>
+      </c>
+      <c r="T67" s="4">
+        <v>6</v>
+      </c>
+      <c r="U67" s="4">
+        <v>3</v>
+      </c>
+      <c r="V67" s="4">
+        <v>3</v>
+      </c>
+      <c r="W67" s="4">
+        <v>4</v>
+      </c>
+      <c r="X67" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y67" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC67" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>403420359</v>
       </c>
@@ -2359,7 +6863,7 @@
       <c r="D68">
         <v>850644378</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="3">
         <v>45916</v>
       </c>
       <c r="F68" t="s">
@@ -2368,8 +6872,74 @@
       <c r="G68" t="s">
         <v>98</v>
       </c>
+      <c r="H68" s="4">
+        <v>3</v>
+      </c>
+      <c r="I68" s="4">
+        <v>5</v>
+      </c>
+      <c r="J68" s="4">
+        <v>7</v>
+      </c>
+      <c r="K68" s="4">
+        <v>5</v>
+      </c>
+      <c r="L68" s="4">
+        <v>5</v>
+      </c>
+      <c r="M68" s="4">
+        <v>3</v>
+      </c>
+      <c r="N68" s="4">
+        <v>4</v>
+      </c>
+      <c r="O68" s="4">
+        <v>2</v>
+      </c>
+      <c r="P68" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>4</v>
+      </c>
+      <c r="R68" s="4">
+        <v>3</v>
+      </c>
+      <c r="S68" s="4">
+        <v>5</v>
+      </c>
+      <c r="T68" s="4">
+        <v>4</v>
+      </c>
+      <c r="U68" s="4">
+        <v>3</v>
+      </c>
+      <c r="V68" s="4">
+        <v>3</v>
+      </c>
+      <c r="W68" s="4">
+        <v>4</v>
+      </c>
+      <c r="X68" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y68" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z68" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA68" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB68" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC68" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>401485187</v>
       </c>
@@ -2382,8 +6952,8 @@
       <c r="D69">
         <v>850644378</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>120</v>
+      <c r="E69" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="F69" t="s">
         <v>94</v>
@@ -2391,8 +6961,95 @@
       <c r="G69" t="s">
         <v>98</v>
       </c>
+      <c r="H69" s="4">
+        <v>3</v>
+      </c>
+      <c r="I69" s="4">
+        <v>5</v>
+      </c>
+      <c r="J69" s="4">
+        <v>7</v>
+      </c>
+      <c r="K69" s="4">
+        <v>5</v>
+      </c>
+      <c r="L69" s="4">
+        <v>5</v>
+      </c>
+      <c r="M69" s="4">
+        <v>3</v>
+      </c>
+      <c r="N69" s="4">
+        <v>4</v>
+      </c>
+      <c r="O69" s="4">
+        <v>2</v>
+      </c>
+      <c r="P69" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>4</v>
+      </c>
+      <c r="R69" s="4">
+        <v>3</v>
+      </c>
+      <c r="S69" s="4">
+        <v>5</v>
+      </c>
+      <c r="T69" s="4">
+        <v>4</v>
+      </c>
+      <c r="U69" s="4">
+        <v>3</v>
+      </c>
+      <c r="V69" s="4">
+        <v>3</v>
+      </c>
+      <c r="W69" s="4">
+        <v>4</v>
+      </c>
+      <c r="X69" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y69" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z69" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA69" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB69" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC69" s="4">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="6">
+    <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="العلامة من 3" sqref="X2:Y69 U2:V69" xr:uid="{596C91A8-3FFB-40A1-867F-8E3707CB5A5D}">
+      <formula1>3</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="العلامة من 5" sqref="H2:H69 M2:M69" xr:uid="{6C63E218-00C5-48C1-B725-D3BAEFA9F467}">
+      <formula1>5</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="العلامة من 6" sqref="S2:T69 P2:Q69" xr:uid="{C7224B71-9CB1-45AD-9234-4CA01AB84A0B}">
+      <formula1>6</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="العلامة من 4" sqref="Z2:Z69 W2:W69 R2:R69 N2:O69" xr:uid="{0380F939-4B65-46F0-95E5-C66243956001}">
+      <formula1>4</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="العلامة من 2" sqref="AA2:AC69" xr:uid="{3EC0E0E0-4FDE-4DE1-9591-FA0A9F677C7A}">
+      <formula1>2</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="العلامة من 7" sqref="I2:L27 K28:L28 I28 I29:L69" xr:uid="{47D191AB-D302-4D56-A84B-7B2FC730F261}">
+      <formula1>7</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>